--- a/inasistencias-5a-TecnicasDigitales/alumnos-5a-TecnicasDigitales.xlsx
+++ b/inasistencias-5a-TecnicasDigitales/alumnos-5a-TecnicasDigitales.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="106">
   <si>
     <t xml:space="preserve">armar grupos y arrancar proyecto</t>
   </si>
@@ -66,6 +66,60 @@
     <t xml:space="preserve">Grupos</t>
   </si>
   <si>
+    <t xml:space="preserve">Joaquin Leandro David</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCARAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49810411@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facundo Gonzalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARREDONDO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arredondofacundo406@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Damian Agustin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coronel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50094499@faa.mil.ar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recursa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santiago Gael</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50157134@gmail.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">Candelaria Luisana</t>
   </si>
   <si>
@@ -75,12 +129,6 @@
     <t xml:space="preserve">49960662@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A</t>
-  </si>
-  <si>
     <t xml:space="preserve">enfermedad</t>
   </si>
   <si>
@@ -96,6 +144,87 @@
     <t xml:space="preserve">50096602@gmail.com</t>
   </si>
   <si>
+    <t xml:space="preserve">Juan Diego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIRALDO GONZALEZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95622238@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demian Ignacio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUNCAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50142917@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeremias Luciano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LESME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jeremiaslesme9@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laionel Dylan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOAIZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50395668@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thiago Valentin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCERO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49602531@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thiago Gabriel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUJAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49927919@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tahiel Eliseo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANRIQUE DI FLORIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50276004@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabrizio Juan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARTINEZ RUIZ DIAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">martnezfabrizio84@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franco Ezequiel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MELIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50353508@gmail.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">Uma Bianca</t>
   </si>
   <si>
@@ -117,6 +246,51 @@
     <t xml:space="preserve">49988641@gmail.com</t>
   </si>
   <si>
+    <t xml:space="preserve">Alejo Julián</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PALERMO TEJADA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">palermoalejo@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mateo Leonel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49880530@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ivan Manuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAVANELLI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49521904@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agustin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ajolote47356@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matias Lionel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAIGUA FRANCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49547928@gmail.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">Giuliana Abril</t>
   </si>
   <si>
@@ -124,180 +298,6 @@
   </si>
   <si>
     <t xml:space="preserve">49676632@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facundo Gonzalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARREDONDO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">arredondofacundo406@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Juan Diego</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GIRALDO GONZALEZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95622238@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laionel Dylan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOAIZA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50395668@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Franco Ezequiel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MELIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50353508@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mateo Leonel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49880530@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joaquin Leandro David</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALCARAZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49810411@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demian Ignacio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUNCAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50142917@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thiago Valentin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUCERO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49602531@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tahiel Eliseo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANRIQUE DI FLORIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50276004@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agustin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Romero</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ajolote47356@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santiago Gael</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIAZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50157134@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thiago Gabriel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUJAN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49927919@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabrizio Juan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARTINEZ RUIZ DIAZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">martnezfabrizio84@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alejo Julián</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PALERMO TEJADA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">palermoalejo@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matias Lionel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAIGUA FRANCO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49547928@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damian Agustin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coronel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50094499@faa.mil.ar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recursa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeremias Luciano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LESME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jeremiaslesme9@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ivan Manuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAVANELLI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49521904@gmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">presentes</t>
@@ -352,8 +352,8 @@
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
-    <numFmt numFmtId="166" formatCode="General"/>
-    <numFmt numFmtId="167" formatCode="hh:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="hh:mm:ss"/>
+    <numFmt numFmtId="167" formatCode="General"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -427,7 +427,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -448,7 +448,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -456,15 +464,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="167" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -481,70 +485,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFF00"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCC0000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCFFCC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFCCCC"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF006600"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -770,9 +711,11 @@
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.07"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="35.71"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="15" min="5" style="1" width="8.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="989" min="989" style="1" width="9.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16350" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="26" min="5" style="1" width="8.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="986" min="986" style="1" width="9.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16348" min="16347" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16352" min="16349" style="0" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16353" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -872,80 +815,74 @@
         <v>46206</v>
       </c>
       <c r="AD2" s="3" t="n">
-        <v>46213</v>
-      </c>
-      <c r="AE2" s="3" t="n">
-        <v>46220</v>
+        <v>46241</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>46227</v>
+        <v>46248</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>46234</v>
+        <v>46255</v>
       </c>
       <c r="AH2" s="3" t="n">
-        <v>46241</v>
+        <v>46262</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>46248</v>
+        <v>46269</v>
       </c>
       <c r="AJ2" s="3" t="n">
-        <v>46255</v>
+        <v>46276</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>46262</v>
+        <v>46283</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>46269</v>
+        <v>46290</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>46276</v>
+        <v>46297</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>46283</v>
+        <v>46304</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>46290</v>
+        <v>46311</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>46297</v>
+        <v>46318</v>
       </c>
       <c r="AQ2" s="3" t="n">
-        <v>46304</v>
+        <v>46325</v>
       </c>
       <c r="AR2" s="3" t="n">
-        <v>46311</v>
+        <v>46332</v>
       </c>
       <c r="AS2" s="3" t="n">
-        <v>46318</v>
+        <v>46339</v>
       </c>
       <c r="AT2" s="3" t="n">
-        <v>46325</v>
+        <v>46346</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46332</v>
+        <v>46353</v>
       </c>
       <c r="AV2" s="3" t="n">
-        <v>46339</v>
+        <v>46360</v>
       </c>
       <c r="AW2" s="3" t="n">
-        <v>46346</v>
+        <v>46367</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>46353</v>
+        <v>46374</v>
       </c>
       <c r="AY2" s="3" t="n">
-        <v>46360</v>
-      </c>
-      <c r="AZ2" s="3" t="n">
-        <v>46367</v>
-      </c>
-      <c r="BA2" s="3" t="n">
-        <v>46374</v>
-      </c>
-      <c r="BB2" s="3" t="n">
         <v>46381</v>
       </c>
+      <c r="AZ2" s="3"/>
+      <c r="BA2" s="3"/>
+      <c r="BB2" s="3"/>
       <c r="BC2" s="3"/>
       <c r="BD2" s="3"/>
       <c r="BE2" s="3"/>
@@ -991,13 +928,10 @@
       <c r="CS2" s="3"/>
       <c r="CT2" s="3"/>
       <c r="CU2" s="3"/>
-      <c r="CV2" s="3"/>
-      <c r="CW2" s="3"/>
-      <c r="CX2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>13</v>
@@ -1012,10 +946,13 @@
         <v>16</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>0.513888888888889</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>16</v>
@@ -1024,7 +961,7 @@
         <v>16</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>16</v>
@@ -1032,19 +969,17 @@
       <c r="N3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>18</v>
-      </c>
+      <c r="O3" s="2"/>
       <c r="P3" s="2" t="s">
         <v>16</v>
       </c>
       <c r="Q3" s="2" t="n">
         <f aca="false">COUNTIF(E3:P3,"P")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R3" s="2" t="n">
         <f aca="false">COUNTIF(E3:P3,"M")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S3" s="2" t="n">
         <f aca="false">COUNTIF(E3:P3,"T")</f>
@@ -1058,26 +993,35 @@
         <f aca="false">SUM(Q3:T3)</f>
         <v>9</v>
       </c>
-      <c r="V3" s="4" t="n">
+      <c r="V3" s="5" t="n">
         <f aca="false">ROUND((Q3+R3/2+S3/4)*10/U3,0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="Z3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="5" t="s">
+      <c r="AC3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD3" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>20</v>
@@ -1136,69 +1080,78 @@
         <f aca="false">SUM(Q4:T4)</f>
         <v>9</v>
       </c>
-      <c r="V4" s="4" t="n">
+      <c r="V4" s="5" t="n">
         <f aca="false">ROUND((Q4+R4/2+S4/4)*10/U4,0)</f>
         <v>10</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Z4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="Z4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD4" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="s">
-        <v>16</v>
+      <c r="E5" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="Q5" s="1" t="n">
         <f aca="false">COUNTIF(E5:P5,"P")</f>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R5" s="1" t="n">
         <f aca="false">COUNTIF(E5:P5,"M")</f>
@@ -1210,33 +1163,41 @@
       </c>
       <c r="T5" s="1" t="n">
         <f aca="false">COUNTIF(E5:P5,"A")</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U5" s="1" t="n">
         <f aca="false">SUM(Q5:T5)</f>
         <v>9</v>
       </c>
-      <c r="V5" s="4" t="n">
+      <c r="V5" s="5" t="n">
         <f aca="false">ROUND((Q5+R5/2+S5/4)*10/U5,0)</f>
-        <v>10</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="X5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="ALA5" s="7"/>
-      <c r="XDV5" s="7"/>
-      <c r="XDW5" s="7"/>
-      <c r="XDX5" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="W5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="X5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AKX5" s="7"/>
+      <c r="XDS5" s="7"/>
+      <c r="XDT5" s="7"/>
+      <c r="XDU5" s="0"/>
+      <c r="XDV5" s="0"/>
+      <c r="XDW5" s="0"/>
+      <c r="XDX5" s="0"/>
       <c r="XDY5" s="7"/>
       <c r="XDZ5" s="7"/>
       <c r="XEA5" s="7"/>
@@ -1272,16 +1233,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>16</v>
@@ -1292,16 +1253,14 @@
       <c r="G6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>16</v>
@@ -1313,56 +1272,64 @@
       <c r="P6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q6" s="1" t="n">
+      <c r="Q6" s="2" t="n">
         <f aca="false">COUNTIF(E6:P6,"P")</f>
-        <v>9</v>
-      </c>
-      <c r="R6" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="R6" s="2" t="n">
         <f aca="false">COUNTIF(E6:P6,"M")</f>
         <v>0</v>
       </c>
-      <c r="S6" s="1" t="n">
+      <c r="S6" s="2" t="n">
         <f aca="false">COUNTIF(E6:P6,"T")</f>
         <v>0</v>
       </c>
-      <c r="T6" s="1" t="n">
+      <c r="T6" s="2" t="n">
         <f aca="false">COUNTIF(E6:P6,"A")</f>
-        <v>0</v>
-      </c>
-      <c r="U6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" s="2" t="n">
         <f aca="false">SUM(Q6:T6)</f>
         <v>9</v>
       </c>
-      <c r="V6" s="4" t="n">
+      <c r="V6" s="5" t="n">
         <f aca="false">ROUND((Q6+R6/2+S6/4)*10/U6,0)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y6" s="2"/>
-      <c r="Z6" s="2" t="n">
-        <v>1</v>
+      <c r="Z6" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="AA6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD6" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>16</v>
@@ -1371,33 +1338,32 @@
         <v>16</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" s="8" t="n">
-        <v>0.583333333333333</v>
+        <v>16</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="O7" s="2"/>
+        <v>16</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="P7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="Q7" s="2" t="n">
         <f aca="false">COUNTIF(E7:P7,"P")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R7" s="2" t="n">
         <f aca="false">COUNTIF(E7:P7,"M")</f>
@@ -1405,45 +1371,54 @@
       </c>
       <c r="S7" s="2" t="n">
         <f aca="false">COUNTIF(E7:P7,"T")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" s="2" t="n">
         <f aca="false">COUNTIF(E7:P7,"A")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U7" s="2" t="n">
         <f aca="false">SUM(Q7:T7)</f>
         <v>9</v>
       </c>
-      <c r="V7" s="4" t="n">
+      <c r="V7" s="5" t="n">
         <f aca="false">ROUND((Q7+R7/2+S7/4)*10/U7,0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD7" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>16</v>
@@ -1493,20 +1468,29 @@
         <f aca="false">SUM(Q8:T8)</f>
         <v>9</v>
       </c>
-      <c r="V8" s="4" t="n">
+      <c r="V8" s="5" t="n">
         <f aca="false">ROUND((Q8+R8/2+S8/4)*10/U8,0)</f>
         <v>10</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Z8" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA8" s="5" t="s">
+      <c r="Z8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD8" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1515,13 +1499,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>16</v>
@@ -1571,7 +1555,7 @@
         <f aca="false">SUM(Q9:T9)</f>
         <v>9</v>
       </c>
-      <c r="V9" s="4" t="n">
+      <c r="V9" s="5" t="n">
         <f aca="false">ROUND((Q9+R9/2+S9/4)*10/U9,0)</f>
         <v>10</v>
       </c>
@@ -1579,9 +1563,9 @@
         <v>16</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y9" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y9" s="4" t="n">
         <v>0.534722222222222</v>
       </c>
       <c r="Z9" s="1" t="n">
@@ -1590,19 +1574,28 @@
       <c r="AA9" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="AB9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD9" s="6" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>16</v>
@@ -1617,10 +1610,7 @@
         <v>16</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K10" s="8" t="n">
-        <v>0.538194444444444</v>
+        <v>16</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>16</v>
@@ -1637,7 +1627,7 @@
       </c>
       <c r="Q10" s="2" t="n">
         <f aca="false">COUNTIF(E10:P10,"P")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R10" s="2" t="n">
         <f aca="false">COUNTIF(E10:P10,"M")</f>
@@ -1645,7 +1635,7 @@
       </c>
       <c r="S10" s="2" t="n">
         <f aca="false">COUNTIF(E10:P10,"T")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" s="2" t="n">
         <f aca="false">COUNTIF(E10:P10,"A")</f>
@@ -1655,107 +1645,124 @@
         <f aca="false">SUM(Q10:T10)</f>
         <v>9</v>
       </c>
-      <c r="V10" s="4" t="n">
+      <c r="V10" s="5" t="n">
         <f aca="false">ROUND((Q10+R10/2+S10/4)*10/U10,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z10" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA10" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z10" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD10" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q11" s="1" t="n">
+      <c r="C11" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q11" s="8" t="n">
         <f aca="false">COUNTIF(E11:P11,"P")</f>
-        <v>9</v>
-      </c>
-      <c r="R11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" s="8" t="n">
         <f aca="false">COUNTIF(E11:P11,"M")</f>
         <v>0</v>
       </c>
-      <c r="S11" s="1" t="n">
+      <c r="S11" s="8" t="n">
         <f aca="false">COUNTIF(E11:P11,"T")</f>
         <v>0</v>
       </c>
-      <c r="T11" s="1" t="n">
+      <c r="T11" s="8" t="n">
         <f aca="false">COUNTIF(E11:P11,"A")</f>
-        <v>0</v>
-      </c>
-      <c r="U11" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="U11" s="8" t="n">
         <f aca="false">SUM(Q11:T11)</f>
         <v>9</v>
       </c>
-      <c r="V11" s="4" t="n">
+      <c r="V11" s="9" t="n">
         <f aca="false">ROUND((Q11+R11/2+S11/4)*10/U11,0)</f>
-        <v>10</v>
-      </c>
-      <c r="W11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="X11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y11" s="1"/>
-      <c r="Z11" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="ALA11" s="7"/>
-      <c r="XDV11" s="7"/>
-      <c r="XDW11" s="7"/>
-      <c r="XDX11" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="W11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="X11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AKX11" s="7"/>
+      <c r="XDS11" s="7"/>
+      <c r="XDT11" s="7"/>
+      <c r="XDU11" s="0"/>
+      <c r="XDV11" s="0"/>
+      <c r="XDW11" s="0"/>
+      <c r="XDX11" s="0"/>
       <c r="XDY11" s="7"/>
       <c r="XDZ11" s="7"/>
       <c r="XEA11" s="7"/>
@@ -1791,33 +1798,33 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K12" s="8" t="n">
+      <c r="K12" s="4" t="n">
         <v>0.538194444444444</v>
       </c>
       <c r="L12" s="2" t="s">
@@ -1827,7 +1834,7 @@
         <v>16</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2" t="s">
@@ -1835,7 +1842,7 @@
       </c>
       <c r="Q12" s="2" t="n">
         <f aca="false">COUNTIF(E12:P12,"P")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R12" s="2" t="n">
         <f aca="false">COUNTIF(E12:P12,"M")</f>
@@ -1847,41 +1854,50 @@
       </c>
       <c r="T12" s="2" t="n">
         <f aca="false">COUNTIF(E12:P12,"A")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12" s="2" t="n">
         <f aca="false">SUM(Q12:T12)</f>
         <v>9</v>
       </c>
-      <c r="V12" s="4" t="n">
+      <c r="V12" s="5" t="n">
         <f aca="false">ROUND((Q12+R12/2+S12/4)*10/U12,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12" s="2" t="s">
         <v>16</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z12" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AA12" s="5" t="s">
+      <c r="AA12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD12" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>16</v>
@@ -1890,10 +1906,7 @@
         <v>17</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>0.513888888888889</v>
+        <v>17</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>16</v>
@@ -1908,19 +1921,19 @@
         <v>16</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q13" s="2" t="n">
         <f aca="false">COUNTIF(E13:P13,"P")</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R13" s="2" t="n">
         <f aca="false">COUNTIF(E13:P13,"M")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" s="2" t="n">
         <f aca="false">COUNTIF(E13:P13,"T")</f>
@@ -1928,15 +1941,15 @@
       </c>
       <c r="T13" s="2" t="n">
         <f aca="false">COUNTIF(E13:P13,"A")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U13" s="2" t="n">
         <f aca="false">SUM(Q13:T13)</f>
         <v>9</v>
       </c>
-      <c r="V13" s="4" t="n">
+      <c r="V13" s="5" t="n">
         <f aca="false">ROUND((Q13+R13/2+S13/4)*10/U13,0)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W13" s="2" t="s">
         <v>17</v>
@@ -1944,25 +1957,34 @@
       <c r="X13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Z13" s="0" t="n">
+      <c r="Z13" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AA13" s="5" t="s">
+      <c r="AA13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD13" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>16</v>
@@ -1971,7 +1993,10 @@
         <v>16</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>0.520833333333333</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>16</v>
@@ -1980,10 +2005,10 @@
         <v>16</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>16</v>
@@ -1994,11 +2019,11 @@
       </c>
       <c r="Q14" s="2" t="n">
         <f aca="false">COUNTIF(E14:P14,"P")</f>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="R14" s="2" t="n">
         <f aca="false">COUNTIF(E14:P14,"M")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="2" t="n">
         <f aca="false">COUNTIF(E14:P14,"T")</f>
@@ -2006,15 +2031,15 @@
       </c>
       <c r="T14" s="2" t="n">
         <f aca="false">COUNTIF(E14:P14,"A")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U14" s="2" t="n">
         <f aca="false">SUM(Q14:T14)</f>
         <v>9</v>
       </c>
-      <c r="V14" s="4" t="n">
+      <c r="V14" s="5" t="n">
         <f aca="false">ROUND((Q14+R14/2+S14/4)*10/U14,0)</f>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W14" s="2" t="s">
         <v>16</v>
@@ -2022,43 +2047,50 @@
       <c r="X14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Z14" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA14" s="5" t="s">
-        <v>16</v>
+      <c r="Z14" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD14" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="1"/>
+        <v>16</v>
+      </c>
       <c r="I15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K15" s="1"/>
       <c r="L15" s="2" t="s">
         <v>16</v>
       </c>
@@ -2066,48 +2098,62 @@
         <v>16</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q15" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q15" s="1" t="n">
         <f aca="false">COUNTIF(E15:P15,"P")</f>
-        <v>5</v>
-      </c>
-      <c r="R15" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="R15" s="1" t="n">
         <f aca="false">COUNTIF(E15:P15,"M")</f>
         <v>0</v>
       </c>
-      <c r="S15" s="2" t="n">
+      <c r="S15" s="1" t="n">
         <f aca="false">COUNTIF(E15:P15,"T")</f>
         <v>0</v>
       </c>
-      <c r="T15" s="2" t="n">
+      <c r="T15" s="1" t="n">
         <f aca="false">COUNTIF(E15:P15,"A")</f>
-        <v>4</v>
-      </c>
-      <c r="U15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="1" t="n">
         <f aca="false">SUM(Q15:T15)</f>
         <v>9</v>
       </c>
-      <c r="V15" s="4" t="n">
+      <c r="V15" s="5" t="n">
         <f aca="false">ROUND((Q15+R15/2+S15/4)*10/U15,0)</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y15" s="0"/>
-      <c r="Z15" s="0" t="n">
+      <c r="Z15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="AA15" s="5" t="s">
-        <v>17</v>
-      </c>
+      <c r="AA15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE15" s="10" t="n">
+        <v>0.541666666666667</v>
+      </c>
+      <c r="AKX15" s="1"/>
+      <c r="AKY15" s="1"/>
+      <c r="AKZ15" s="1"/>
       <c r="ALA15" s="1"/>
       <c r="ALB15" s="1"/>
       <c r="ALC15" s="1"/>
@@ -2150,58 +2196,56 @@
       <c r="AMN15" s="1"/>
       <c r="AMO15" s="1"/>
       <c r="AMP15" s="1"/>
-      <c r="AMQ15" s="1"/>
-      <c r="AMR15" s="1"/>
-      <c r="AMS15" s="1"/>
-      <c r="XDV15" s="1"/>
-      <c r="XDW15" s="1"/>
+      <c r="XDS15" s="1"/>
+      <c r="XDT15" s="1"/>
+      <c r="XDU15" s="0"/>
+      <c r="XDV15" s="0"/>
+      <c r="XDW15" s="0"/>
+      <c r="XDX15" s="0"/>
     </row>
     <row r="16" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2" t="s">
+      <c r="F16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2" t="s">
+      <c r="N16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="Q16" s="1" t="n">
         <f aca="false">COUNTIF(E16:P16,"P")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R16" s="1" t="n">
         <f aca="false">COUNTIF(E16:P16,"M")</f>
@@ -2213,124 +2257,144 @@
       </c>
       <c r="T16" s="1" t="n">
         <f aca="false">COUNTIF(E16:P16,"A")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U16" s="1" t="n">
         <f aca="false">SUM(Q16:T16)</f>
         <v>9</v>
       </c>
-      <c r="V16" s="4" t="n">
+      <c r="V16" s="5" t="n">
         <f aca="false">ROUND((Q16+R16/2+S16/4)*10/U16,0)</f>
-        <v>10</v>
-      </c>
-      <c r="W16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="X16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y16" s="2"/>
-      <c r="Z16" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA16" s="2" t="s">
-        <v>16</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="W16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z16" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="XDU16" s="0"/>
+      <c r="XDV16" s="0"/>
+      <c r="XDW16" s="0"/>
+      <c r="XDX16" s="0"/>
     </row>
     <row r="17" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K17" s="8" t="n">
-        <v>0.534722222222222</v>
-      </c>
-      <c r="L17" s="2" t="s">
+      <c r="F17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L17" s="1" t="s">
         <v>16</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q17" s="2" t="n">
+      <c r="N17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q17" s="1" t="n">
         <f aca="false">COUNTIF(E17:P17,"P")</f>
-        <v>7</v>
-      </c>
-      <c r="R17" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="R17" s="1" t="n">
         <f aca="false">COUNTIF(E17:P17,"M")</f>
         <v>0</v>
       </c>
-      <c r="S17" s="2" t="n">
+      <c r="S17" s="1" t="n">
         <f aca="false">COUNTIF(E17:P17,"T")</f>
-        <v>1</v>
-      </c>
-      <c r="T17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="1" t="n">
         <f aca="false">COUNTIF(E17:P17,"A")</f>
-        <v>1</v>
-      </c>
-      <c r="U17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="1" t="n">
         <f aca="false">SUM(Q17:T17)</f>
         <v>9</v>
       </c>
-      <c r="V17" s="4" t="n">
+      <c r="V17" s="5" t="n">
         <f aca="false">ROUND((Q17+R17/2+S17/4)*10/U17,0)</f>
-        <v>8</v>
-      </c>
-      <c r="W17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="X17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y17" s="0"/>
-      <c r="Z17" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA17" s="5" t="s">
-        <v>17</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="W17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z17" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="XDU17" s="0"/>
+      <c r="XDV17" s="0"/>
+      <c r="XDW17" s="0"/>
+      <c r="XDX17" s="0"/>
     </row>
     <row r="18" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>16</v>
@@ -2341,16 +2405,14 @@
       <c r="G18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H18" s="1"/>
       <c r="I18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K18" s="1"/>
       <c r="L18" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>16</v>
@@ -2361,43 +2423,54 @@
       <c r="P18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q18" s="2" t="n">
+      <c r="Q18" s="1" t="n">
         <f aca="false">COUNTIF(E18:P18,"P")</f>
-        <v>8</v>
-      </c>
-      <c r="R18" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="R18" s="1" t="n">
         <f aca="false">COUNTIF(E18:P18,"M")</f>
         <v>0</v>
       </c>
-      <c r="S18" s="2" t="n">
+      <c r="S18" s="1" t="n">
         <f aca="false">COUNTIF(E18:P18,"T")</f>
         <v>0</v>
       </c>
-      <c r="T18" s="2" t="n">
+      <c r="T18" s="1" t="n">
         <f aca="false">COUNTIF(E18:P18,"A")</f>
-        <v>1</v>
-      </c>
-      <c r="U18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="1" t="n">
         <f aca="false">SUM(Q18:T18)</f>
         <v>9</v>
       </c>
-      <c r="V18" s="4" t="n">
+      <c r="V18" s="5" t="n">
         <f aca="false">ROUND((Q18+R18/2+S18/4)*10/U18,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="X18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y18" s="0"/>
-      <c r="Z18" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA18" s="5" t="s">
-        <v>16</v>
-      </c>
+      <c r="Z18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AKX18" s="1"/>
+      <c r="AKY18" s="1"/>
+      <c r="AKZ18" s="1"/>
       <c r="ALA18" s="1"/>
       <c r="ALB18" s="1"/>
       <c r="ALC18" s="1"/>
@@ -2440,24 +2513,25 @@
       <c r="AMN18" s="1"/>
       <c r="AMO18" s="1"/>
       <c r="AMP18" s="1"/>
-      <c r="AMQ18" s="1"/>
-      <c r="AMR18" s="1"/>
-      <c r="AMS18" s="1"/>
-      <c r="XDV18" s="1"/>
-      <c r="XDW18" s="1"/>
+      <c r="XDS18" s="1"/>
+      <c r="XDT18" s="1"/>
+      <c r="XDU18" s="0"/>
+      <c r="XDV18" s="0"/>
+      <c r="XDW18" s="0"/>
+      <c r="XDX18" s="0"/>
     </row>
     <row r="19" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>16</v>
@@ -2466,10 +2540,7 @@
         <v>16</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>0.520833333333333</v>
+        <v>16</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>16</v>
@@ -2477,12 +2548,11 @@
       <c r="J19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="K19" s="1"/>
       <c r="L19" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>16</v>
@@ -2490,43 +2560,54 @@
       <c r="P19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Q19" s="2" t="n">
+      <c r="Q19" s="1" t="n">
         <f aca="false">COUNTIF(E19:P19,"P")</f>
-        <v>6</v>
-      </c>
-      <c r="R19" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="R19" s="1" t="n">
         <f aca="false">COUNTIF(E19:P19,"M")</f>
-        <v>1</v>
-      </c>
-      <c r="S19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="1" t="n">
         <f aca="false">COUNTIF(E19:P19,"T")</f>
         <v>0</v>
       </c>
-      <c r="T19" s="2" t="n">
+      <c r="T19" s="1" t="n">
         <f aca="false">COUNTIF(E19:P19,"A")</f>
-        <v>2</v>
-      </c>
-      <c r="U19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="1" t="n">
         <f aca="false">SUM(Q19:T19)</f>
         <v>9</v>
       </c>
-      <c r="V19" s="4" t="n">
+      <c r="V19" s="5" t="n">
         <f aca="false">ROUND((Q19+R19/2+S19/4)*10/U19,0)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="X19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="Y19" s="0"/>
-      <c r="Z19" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA19" s="5" t="s">
-        <v>16</v>
-      </c>
+      <c r="Z19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AKX19" s="1"/>
+      <c r="AKY19" s="1"/>
+      <c r="AKZ19" s="1"/>
       <c r="ALA19" s="1"/>
       <c r="ALB19" s="1"/>
       <c r="ALC19" s="1"/>
@@ -2569,30 +2650,31 @@
       <c r="AMN19" s="1"/>
       <c r="AMO19" s="1"/>
       <c r="AMP19" s="1"/>
-      <c r="AMQ19" s="1"/>
-      <c r="AMR19" s="1"/>
-      <c r="AMS19" s="1"/>
-      <c r="XDV19" s="1"/>
-      <c r="XDW19" s="1"/>
+      <c r="XDS19" s="1"/>
+      <c r="XDT19" s="1"/>
+      <c r="XDU19" s="0"/>
+      <c r="XDV19" s="0"/>
+      <c r="XDW19" s="0"/>
+      <c r="XDX19" s="0"/>
     </row>
     <row r="20" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>16</v>
@@ -2617,7 +2699,7 @@
       </c>
       <c r="Q20" s="1" t="n">
         <f aca="false">COUNTIF(E20:P20,"P")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R20" s="1" t="n">
         <f aca="false">COUNTIF(E20:P20,"M")</f>
@@ -2629,18 +2711,18 @@
       </c>
       <c r="T20" s="1" t="n">
         <f aca="false">COUNTIF(E20:P20,"A")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U20" s="1" t="n">
         <f aca="false">SUM(Q20:T20)</f>
         <v>9</v>
       </c>
-      <c r="V20" s="4" t="n">
+      <c r="V20" s="5" t="n">
         <f aca="false">ROUND((Q20+R20/2+S20/4)*10/U20,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X20" s="1" t="s">
         <v>16</v>
@@ -2649,171 +2731,204 @@
         <v>4</v>
       </c>
       <c r="AA20" s="1" t="s">
-        <v>17</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="XDU20" s="0"/>
+      <c r="XDV20" s="0"/>
+      <c r="XDW20" s="0"/>
+      <c r="XDX20" s="0"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L21" s="1" t="s">
+      <c r="F21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>0.538194444444444</v>
+      </c>
+      <c r="L21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q21" s="1" t="n">
+      <c r="N21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q21" s="2" t="n">
         <f aca="false">COUNTIF(E21:P21,"P")</f>
-        <v>9</v>
-      </c>
-      <c r="R21" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="R21" s="2" t="n">
         <f aca="false">COUNTIF(E21:P21,"M")</f>
         <v>0</v>
       </c>
-      <c r="S21" s="1" t="n">
+      <c r="S21" s="2" t="n">
         <f aca="false">COUNTIF(E21:P21,"T")</f>
-        <v>0</v>
-      </c>
-      <c r="T21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" s="2" t="n">
         <f aca="false">COUNTIF(E21:P21,"A")</f>
-        <v>0</v>
-      </c>
-      <c r="U21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" s="2" t="n">
         <f aca="false">SUM(Q21:T21)</f>
         <v>9</v>
       </c>
-      <c r="V21" s="4" t="n">
+      <c r="V21" s="5" t="n">
         <f aca="false">ROUND((Q21+R21/2+S21/4)*10/U21,0)</f>
-        <v>10</v>
-      </c>
-      <c r="W21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="X21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y21" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="X21" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="Z21" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD21" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="P22" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q22" s="8" t="n">
+        <f aca="false">COUNTIF(E22:P22,"P")</f>
+        <v>5</v>
+      </c>
+      <c r="R22" s="8" t="n">
+        <f aca="false">COUNTIF(E22:P22,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="S22" s="8" t="n">
+        <f aca="false">COUNTIF(E22:P22,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="T22" s="8" t="n">
+        <f aca="false">COUNTIF(E22:P22,"A")</f>
         <v>4</v>
       </c>
-      <c r="AA21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" s="6" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q22" s="1" t="n">
-        <f aca="false">COUNTIF(E22:P22,"P")</f>
-        <v>9</v>
-      </c>
-      <c r="R22" s="1" t="n">
-        <f aca="false">COUNTIF(E22:P22,"M")</f>
-        <v>0</v>
-      </c>
-      <c r="S22" s="1" t="n">
-        <f aca="false">COUNTIF(E22:P22,"T")</f>
-        <v>0</v>
-      </c>
-      <c r="T22" s="1" t="n">
-        <f aca="false">COUNTIF(E22:P22,"A")</f>
-        <v>0</v>
-      </c>
-      <c r="U22" s="1" t="n">
+      <c r="U22" s="8" t="n">
         <f aca="false">SUM(Q22:T22)</f>
         <v>9</v>
       </c>
-      <c r="V22" s="4" t="n">
+      <c r="V22" s="9" t="n">
         <f aca="false">ROUND((Q22+R22/2+S22/4)*10/U22,0)</f>
-        <v>10</v>
-      </c>
-      <c r="W22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="X22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Y22" s="2"/>
-      <c r="Z22" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="ALA22" s="7"/>
-      <c r="XDV22" s="7"/>
-      <c r="XDW22" s="7"/>
-      <c r="XDX22" s="7"/>
+        <v>6</v>
+      </c>
+      <c r="W22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="X22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AKX22" s="7"/>
+      <c r="XDS22" s="7"/>
+      <c r="XDT22" s="7"/>
+      <c r="XDU22" s="0"/>
+      <c r="XDV22" s="0"/>
+      <c r="XDW22" s="0"/>
+      <c r="XDX22" s="0"/>
       <c r="XDY22" s="7"/>
       <c r="XDZ22" s="7"/>
       <c r="XEA22" s="7"/>
@@ -2848,166 +2963,183 @@
       <c r="XFD22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>0.534722222222222</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <f aca="false">COUNTIF(E23:P23,"P")</f>
+        <v>7</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <f aca="false">COUNTIF(E23:P23,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <f aca="false">COUNTIF(E23:P23,"T")</f>
+        <v>1</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <f aca="false">COUNTIF(E23:P23,"A")</f>
+        <v>1</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <f aca="false">SUM(Q23:T23)</f>
+        <v>9</v>
+      </c>
+      <c r="V23" s="5" t="n">
+        <f aca="false">ROUND((Q23+R23/2+S23/4)*10/U23,0)</f>
+        <v>8</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z23" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="M23" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="N23" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q23" s="1" t="n">
-        <f aca="false">COUNTIF(E23:P23,"P")</f>
-        <v>1</v>
-      </c>
-      <c r="R23" s="1" t="n">
-        <f aca="false">COUNTIF(E23:P23,"M")</f>
-        <v>0</v>
-      </c>
-      <c r="S23" s="1" t="n">
-        <f aca="false">COUNTIF(E23:P23,"T")</f>
-        <v>0</v>
-      </c>
-      <c r="T23" s="1" t="n">
-        <f aca="false">COUNTIF(E23:P23,"A")</f>
-        <v>8</v>
-      </c>
-      <c r="U23" s="1" t="n">
-        <f aca="false">SUM(Q23:T23)</f>
-        <v>9</v>
-      </c>
-      <c r="V23" s="4" t="n">
-        <f aca="false">ROUND((Q23+R23/2+S23/4)*10/U23,0)</f>
-        <v>1</v>
-      </c>
-      <c r="W23" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="X23" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y23" s="6"/>
-      <c r="Z23" s="6"/>
-      <c r="AA23" s="6" t="s">
-        <v>84</v>
+      <c r="AA23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD23" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B24" s="7" t="s">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="M24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="N24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q24" s="6" t="n">
+      <c r="E24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q24" s="1" t="n">
         <f aca="false">COUNTIF(E24:P24,"P")</f>
-        <v>1</v>
-      </c>
-      <c r="R24" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="R24" s="1" t="n">
         <f aca="false">COUNTIF(E24:P24,"M")</f>
         <v>0</v>
       </c>
-      <c r="S24" s="6" t="n">
+      <c r="S24" s="1" t="n">
         <f aca="false">COUNTIF(E24:P24,"T")</f>
         <v>0</v>
       </c>
-      <c r="T24" s="6" t="n">
+      <c r="T24" s="1" t="n">
         <f aca="false">COUNTIF(E24:P24,"A")</f>
-        <v>8</v>
-      </c>
-      <c r="U24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="1" t="n">
         <f aca="false">SUM(Q24:T24)</f>
         <v>9</v>
       </c>
-      <c r="V24" s="9" t="n">
+      <c r="V24" s="5" t="n">
         <f aca="false">ROUND((Q24+R24/2+S24/4)*10/U24,0)</f>
-        <v>1</v>
-      </c>
-      <c r="W24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="X24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AA24" s="6" t="s">
-        <v>17</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="X24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AKX24" s="1"/>
+      <c r="AKY24" s="1"/>
+      <c r="AKZ24" s="1"/>
       <c r="ALA24" s="1"/>
       <c r="ALB24" s="1"/>
       <c r="ALC24" s="1"/>
@@ -3050,91 +3182,101 @@
       <c r="AMN24" s="1"/>
       <c r="AMO24" s="1"/>
       <c r="AMP24" s="1"/>
-      <c r="AMQ24" s="1"/>
-      <c r="AMR24" s="1"/>
-      <c r="AMS24" s="1"/>
-      <c r="XDV24" s="1"/>
-      <c r="XDW24" s="1"/>
+      <c r="XDS24" s="1"/>
+      <c r="XDT24" s="1"/>
+      <c r="XDU24" s="0"/>
+      <c r="XDV24" s="0"/>
+      <c r="XDW24" s="0"/>
+      <c r="XDX24" s="0"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B25" s="7" t="s">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="K25" s="6"/>
-      <c r="L25" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="M25" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="N25" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q25" s="6" t="n">
+      <c r="E25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q25" s="2" t="n">
         <f aca="false">COUNTIF(E25:P25,"P")</f>
-        <v>5</v>
-      </c>
-      <c r="R25" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R25" s="2" t="n">
         <f aca="false">COUNTIF(E25:P25,"M")</f>
         <v>0</v>
       </c>
-      <c r="S25" s="6" t="n">
+      <c r="S25" s="2" t="n">
         <f aca="false">COUNTIF(E25:P25,"T")</f>
-        <v>0</v>
-      </c>
-      <c r="T25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" s="2" t="n">
         <f aca="false">COUNTIF(E25:P25,"A")</f>
-        <v>4</v>
-      </c>
-      <c r="U25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" s="2" t="n">
         <f aca="false">SUM(Q25:T25)</f>
         <v>9</v>
       </c>
-      <c r="V25" s="9" t="n">
+      <c r="V25" s="5" t="n">
         <f aca="false">ROUND((Q25+R25/2+S25/4)*10/U25,0)</f>
-        <v>6</v>
-      </c>
-      <c r="W25" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="X25" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y25" s="6"/>
-      <c r="Z25" s="6"/>
-      <c r="AA25" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
+      </c>
+      <c r="W25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="X25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z25" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD25" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3177,12 +3319,6 @@
         <f aca="false">COUNTIF(P3:P25,"P")</f>
         <v>19</v>
       </c>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
       <c r="W26" s="1" t="n">
         <f aca="false">COUNTIF(W3:W25,"P")</f>
         <v>12</v>
@@ -3191,12 +3327,23 @@
         <f aca="false">COUNTIF(X3:X25,"P")</f>
         <v>17</v>
       </c>
-      <c r="Y26" s="1"/>
-      <c r="Z26" s="1"/>
       <c r="AA26" s="1" t="n">
         <f aca="false">COUNTIF(AA3:AA25,"P")</f>
         <v>16</v>
       </c>
+      <c r="AB26" s="1" t="n">
+        <f aca="false">COUNTIF(AB3:AB25,"P")</f>
+        <v>16</v>
+      </c>
+      <c r="AC26" s="1" t="n">
+        <f aca="false">COUNTIF(AC3:AC25,"P")</f>
+        <v>12</v>
+      </c>
+      <c r="AD26" s="1" t="n">
+        <f aca="false">COUNTIF(AD3:AD25,"P")</f>
+        <v>16</v>
+      </c>
+      <c r="AE26" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="1" t="s">
@@ -3259,6 +3406,19 @@
         <f aca="false">COUNTIF(AA3:AA25,"M")</f>
         <v>0</v>
       </c>
+      <c r="AB27" s="2" t="n">
+        <f aca="false">COUNTIF(AB3:AB25,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AC27" s="2" t="n">
+        <f aca="false">COUNTIF(AC3:AC25,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AD27" s="2" t="n">
+        <f aca="false">COUNTIF(AD3:AD25,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AE27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
@@ -3317,7 +3477,23 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
-      <c r="AA28" s="2"/>
+      <c r="AA28" s="2" t="n">
+        <f aca="false">COUNTIF(AA3:AA25,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AB28" s="2" t="n">
+        <f aca="false">COUNTIF(AB3:AB25,"T")</f>
+        <v>1</v>
+      </c>
+      <c r="AC28" s="2" t="n">
+        <f aca="false">COUNTIF(AC3:AC25,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AD28" s="2" t="n">
+        <f aca="false">COUNTIF(AD3:AD25,"T")</f>
+        <v>1</v>
+      </c>
+      <c r="AE28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="1" t="s">
@@ -3380,17 +3556,30 @@
         <f aca="false">SUM(AA26:AA28)</f>
         <v>16</v>
       </c>
+      <c r="AB29" s="2" t="n">
+        <f aca="false">SUM(AB26:AB28)</f>
+        <v>17</v>
+      </c>
+      <c r="AC29" s="2" t="n">
+        <f aca="false">SUM(AC26:AC28)</f>
+        <v>12</v>
+      </c>
+      <c r="AD29" s="2" t="n">
+        <f aca="false">SUM(AD26:AD28)</f>
+        <v>17</v>
+      </c>
+      <c r="AE29" s="2"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="V3:V25">
-    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>4</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>4</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3416,7 +3605,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.36"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="9.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16330" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16332" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3439,15 +3628,21 @@
         <v>96</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>99</v>
       </c>
     </row>
@@ -3456,31 +3651,33 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H3" s="1" t="n">
+      <c r="F3" s="5"/>
+      <c r="G3" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="I3" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I3" s="1" t="n">
+      <c r="J3" s="1"/>
+      <c r="K3" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="J3" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C3,E3,G3,H3,I3),0)</f>
+      <c r="L3" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C3,E3,G3,I3,K3),0)</f>
         <v>8</v>
       </c>
-      <c r="K3" s="1" t="str">
-        <f aca="false">IF(J3&gt;7,"TEA",IF(J3&gt;3,"TEP","TED"))</f>
+      <c r="M3" s="1" t="str">
+        <f aca="false">IF(L3&gt;6,"TEA",IF(L3&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -3489,40 +3686,42 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>9</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5"/>
       <c r="I4" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C4,E4,G4,H4,I4),0)</f>
-        <v>10</v>
-      </c>
-      <c r="K4" s="1" t="str">
-        <f aca="false">IF(J4&gt;7,"TEA",IF(J4&gt;3,"TEP","TED"))</f>
+        <v>9</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C4,E4,G4,I4,K4),0)</f>
+        <v>10</v>
+      </c>
+      <c r="M4" s="1" t="str">
+        <f aca="false">IF(L4&gt;6,"TEA",IF(L4&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
-    <row r="5" s="6" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" s="8" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="n">
         <v>3</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>1</v>
@@ -3535,22 +3734,22 @@
       <c r="G5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="H5" s="9"/>
       <c r="I5" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J5" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C5,E5,G5,H5,I5),0)</f>
-        <v>1</v>
-      </c>
-      <c r="K5" s="7" t="str">
-        <f aca="false">IF(J5&gt;7,"TEA",IF(J5&gt;3,"TEP","TED"))</f>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C5,E5,G5,I5,K5),0)</f>
+        <v>1</v>
+      </c>
+      <c r="M5" s="1" t="str">
+        <f aca="false">IF(L5&gt;6,"TEA",IF(L5&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
-      <c r="XDB5" s="7"/>
-      <c r="XDC5" s="7"/>
       <c r="XDD5" s="7"/>
       <c r="XDE5" s="7"/>
       <c r="XDF5" s="7"/>
@@ -3610,32 +3809,38 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>46171</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4" t="n">
+      <c r="F6" s="5"/>
+      <c r="G6" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H6" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="H6" s="5"/>
       <c r="I6" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C6,E6,G6,H6,I6),0)</f>
-        <v>5</v>
-      </c>
-      <c r="K6" s="1" t="str">
-        <f aca="false">IF(J6&gt;7,"TEA",IF(J6&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+        <v>3</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C6,E6,G6,I6,K6),0)</f>
+        <v>7</v>
+      </c>
+      <c r="M6" s="1" t="str">
+        <f aca="false">IF(L6&gt;6,"TEA",IF(L6&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3643,33 +3848,37 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4" t="n">
-        <v>9</v>
+        <v>32</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5" t="n">
+        <v>8</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>46171</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="G7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" s="5"/>
       <c r="I7" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C7,E7,G7,H7,I7),0)</f>
-        <v>8</v>
-      </c>
-      <c r="K7" s="1" t="str">
-        <f aca="false">IF(J7&gt;7,"TEA",IF(J7&gt;3,"TEP","TED"))</f>
+        <v>7</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>46171</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C7,E7,G7,I7,K7),0)</f>
+        <v>9</v>
+      </c>
+      <c r="M7" s="1" t="str">
+        <f aca="false">IF(L7&gt;6,"TEA",IF(L7&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -3678,31 +3887,33 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>9</v>
-      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" s="5"/>
       <c r="I8" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C8,E8,G8,H8,I8),0)</f>
-        <v>9</v>
-      </c>
-      <c r="K8" s="1" t="str">
-        <f aca="false">IF(J8&gt;7,"TEA",IF(J8&gt;3,"TEP","TED"))</f>
+        <v>9</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C8,E8,G8,I8,K8),0)</f>
+        <v>9</v>
+      </c>
+      <c r="M8" s="1" t="str">
+        <f aca="false">IF(L8&gt;6,"TEA",IF(L8&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -3711,32 +3922,40 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>1</v>
+        <v>40</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>46220</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C9,E9,G9,H9,I9),0)</f>
-        <v>5</v>
-      </c>
-      <c r="K9" s="1" t="str">
-        <f aca="false">IF(J9&gt;7,"TEA",IF(J9&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+        <v>7</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C9,E9,G9,I9,K9),0)</f>
+        <v>8</v>
+      </c>
+      <c r="M9" s="1" t="str">
+        <f aca="false">IF(L9&gt;6,"TEA",IF(L9&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3744,32 +3963,38 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>46171</v>
+      </c>
+      <c r="G10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H10" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="H10" s="5"/>
       <c r="I10" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C10,E10,G10,H10,I10),0)</f>
-        <v>6</v>
-      </c>
-      <c r="K10" s="1" t="str">
-        <f aca="false">IF(J10&gt;7,"TEA",IF(J10&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+        <v>7</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C10,E10,G10,I10,K10),0)</f>
+        <v>8</v>
+      </c>
+      <c r="M10" s="1" t="str">
+        <f aca="false">IF(L10&gt;6,"TEA",IF(L10&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3777,31 +4002,33 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>1</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="5"/>
       <c r="I11" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="J11" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C11,E11,G11,H11,I11),0)</f>
-        <v>1</v>
-      </c>
-      <c r="K11" s="1" t="str">
-        <f aca="false">IF(J11&gt;7,"TEA",IF(J11&gt;3,"TEP","TED"))</f>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C11,E11,G11,I11,K11),0)</f>
+        <v>1</v>
+      </c>
+      <c r="M11" s="1" t="str">
+        <f aca="false">IF(L11&gt;6,"TEA",IF(L11&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
     </row>
@@ -3810,34 +4037,40 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="C12" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>46171</v>
       </c>
-      <c r="E12" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>1</v>
+      <c r="E12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>46220</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="J12" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C12,E12,G12,H12,I12),0)</f>
-        <v>5</v>
-      </c>
-      <c r="K12" s="1" t="str">
-        <f aca="false">IF(J12&gt;7,"TEA",IF(J12&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+        <v>7</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C12,E12,G12,I12,K12),0)</f>
+        <v>8</v>
+      </c>
+      <c r="M12" s="1" t="str">
+        <f aca="false">IF(L12&gt;6,"TEA",IF(L12&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3845,31 +4078,33 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>9</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" s="5"/>
       <c r="I13" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="J13" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C13,E13,G13,H13,I13),0)</f>
-        <v>9</v>
-      </c>
-      <c r="K13" s="1" t="str">
-        <f aca="false">IF(J13&gt;7,"TEA",IF(J13&gt;3,"TEP","TED"))</f>
+      <c r="L13" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C13,E13,G13,I13,K13),0)</f>
+        <v>9</v>
+      </c>
+      <c r="M13" s="1" t="str">
+        <f aca="false">IF(L13&gt;6,"TEA",IF(L13&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -3878,31 +4113,33 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="C14" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>10</v>
-      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" s="5"/>
       <c r="I14" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="J14" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C14,E14,G14,H14,I14),0)</f>
-        <v>9</v>
-      </c>
-      <c r="K14" s="1" t="str">
-        <f aca="false">IF(J14&gt;7,"TEA",IF(J14&gt;3,"TEP","TED"))</f>
+      <c r="L14" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C14,E14,G14,I14,K14),0)</f>
+        <v>9</v>
+      </c>
+      <c r="M14" s="1" t="str">
+        <f aca="false">IF(L14&gt;6,"TEA",IF(L14&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -3911,35 +4148,33 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F15" s="4"/>
+        <v>58</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="5"/>
       <c r="G15" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="I15" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J15" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C15,E15,G15,H15,I15),0)</f>
-        <v>9</v>
-      </c>
-      <c r="K15" s="1" t="str">
-        <f aca="false">IF(J15&gt;7,"TEA",IF(J15&gt;3,"TEP","TED"))</f>
+      <c r="K15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C15,E15,G15,I15,K15),0)</f>
+        <v>9</v>
+      </c>
+      <c r="M15" s="1" t="str">
+        <f aca="false">IF(L15&gt;6,"TEA",IF(L15&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="XCZ15" s="1"/>
-      <c r="XDA15" s="1"/>
       <c r="XDB15" s="1"/>
       <c r="XDC15" s="1"/>
       <c r="XDD15" s="1"/>
@@ -4001,32 +4236,40 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="C16" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="1" t="n">
-        <v>1</v>
+      <c r="D16" s="3" t="n">
+        <v>46171</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>46220</v>
       </c>
       <c r="I16" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="J16" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C16,E16,G16,H16,I16),0)</f>
-        <v>4</v>
-      </c>
-      <c r="K16" s="1" t="str">
-        <f aca="false">IF(J16&gt;7,"TEA",IF(J16&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+        <v>7</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>46220</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C16,E16,G16,I16,K16),0)</f>
+        <v>7</v>
+      </c>
+      <c r="M16" s="1" t="str">
+        <f aca="false">IF(L16&gt;6,"TEA",IF(L16&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4034,31 +4277,34 @@
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>10</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>46171</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" s="5"/>
       <c r="I17" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="J17" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C17,E17,G17,H17,I17),0)</f>
-        <v>8</v>
-      </c>
-      <c r="K17" s="1" t="str">
-        <f aca="false">IF(J17&gt;7,"TEA",IF(J17&gt;3,"TEP","TED"))</f>
+      <c r="K17" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C17,E17,G17,I17,K17),0)</f>
+        <v>9</v>
+      </c>
+      <c r="M17" s="1" t="str">
+        <f aca="false">IF(L17&gt;6,"TEA",IF(L17&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -4067,35 +4313,33 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="C18" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="F18" s="4"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" s="5"/>
       <c r="G18" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="H18" s="2" t="n">
-        <v>9</v>
-      </c>
       <c r="I18" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J18" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C18,E18,G18,H18,I18),0)</f>
-        <v>9</v>
-      </c>
-      <c r="K18" s="1" t="str">
-        <f aca="false">IF(J18&gt;7,"TEA",IF(J18&gt;3,"TEP","TED"))</f>
+        <v>9</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C18,E18,G18,I18,K18),0)</f>
+        <v>9</v>
+      </c>
+      <c r="M18" s="1" t="str">
+        <f aca="false">IF(L18&gt;6,"TEA",IF(L18&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="XCZ18" s="1"/>
-      <c r="XDA18" s="1"/>
       <c r="XDB18" s="1"/>
       <c r="XDC18" s="1"/>
       <c r="XDD18" s="1"/>
@@ -4157,35 +4401,33 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="F19" s="4"/>
+        <v>71</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F19" s="5"/>
       <c r="G19" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H19" s="2" t="n">
-        <v>10</v>
-      </c>
       <c r="I19" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="J19" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C19,E19,G19,H19,I19),0)</f>
-        <v>10</v>
-      </c>
-      <c r="K19" s="1" t="str">
-        <f aca="false">IF(J19&gt;7,"TEA",IF(J19&gt;3,"TEP","TED"))</f>
+      <c r="K19" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C19,E19,G19,I19,K19),0)</f>
+        <v>10</v>
+      </c>
+      <c r="M19" s="1" t="str">
+        <f aca="false">IF(L19&gt;6,"TEA",IF(L19&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-      <c r="XCZ19" s="1"/>
-      <c r="XDA19" s="1"/>
       <c r="XDB19" s="1"/>
       <c r="XDC19" s="1"/>
       <c r="XDD19" s="1"/>
@@ -4247,31 +4489,32 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H20" s="1" t="n">
+      <c r="H20" s="5"/>
+      <c r="I20" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I20" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J20" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C20,E20,G20,H20,I20),0)</f>
-        <v>9</v>
-      </c>
-      <c r="K20" s="1" t="str">
-        <f aca="false">IF(J20&gt;7,"TEA",IF(J20&gt;3,"TEP","TED"))</f>
+      <c r="K20" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C20,E20,G20,I20,K20),0)</f>
+        <v>9</v>
+      </c>
+      <c r="M20" s="1" t="str">
+        <f aca="false">IF(L20&gt;6,"TEA",IF(L20&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -4280,31 +4523,34 @@
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="E21" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>1</v>
-      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="5"/>
       <c r="I21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="J21" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C21,E21,G21,H21,I21),0)</f>
-        <v>4</v>
-      </c>
-      <c r="K21" s="1" t="str">
-        <f aca="false">IF(J21&gt;7,"TEA",IF(J21&gt;3,"TEP","TED"))</f>
+      <c r="L21" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C21,E21,G21,I21,K21),0)</f>
+        <v>5</v>
+      </c>
+      <c r="M21" s="1" t="str">
+        <f aca="false">IF(L21&gt;6,"TEA",IF(L21&gt;3,"TEP","TED"))</f>
         <v>TEP</v>
       </c>
     </row>
@@ -4313,7 +4559,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C22" s="9" t="n">
         <v>1</v>
@@ -4326,18 +4572,19 @@
       <c r="G22" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="H22" s="9"/>
       <c r="I22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="J22" s="7" t="n">
-        <f aca="false">ROUND(AVERAGE(C22,E22,G22,H22,I22),0)</f>
+      <c r="L22" s="7" t="n">
+        <f aca="false">ROUND(AVERAGE(C22,E22,G22,I22,K22),0)</f>
         <v>2</v>
       </c>
-      <c r="K22" s="7" t="str">
-        <f aca="false">IF(J22&gt;7,"TEA",IF(J22&gt;3,"TEP","TED"))</f>
+      <c r="M22" s="1" t="str">
+        <f aca="false">IF(L22&gt;6,"TEA",IF(L22&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
     </row>
@@ -4346,31 +4593,32 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H23" s="1" t="n">
-        <v>10</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H23" s="5"/>
       <c r="I23" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="K23" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="J23" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C23,E23,G23,H23,I23),0)</f>
-        <v>9</v>
-      </c>
-      <c r="K23" s="1" t="str">
-        <f aca="false">IF(J23&gt;7,"TEA",IF(J23&gt;3,"TEP","TED"))</f>
+      <c r="L23" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C23,E23,G23,I23,K23),0)</f>
+        <v>9</v>
+      </c>
+      <c r="M23" s="1" t="str">
+        <f aca="false">IF(L23&gt;6,"TEA",IF(L23&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
     </row>
@@ -4379,12 +4627,14 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="4"/>
+        <v>86</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>46171</v>
+      </c>
       <c r="E24" s="1" t="n">
         <v>5</v>
       </c>
@@ -4392,22 +4642,20 @@
       <c r="G24" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="H24" s="2" t="n">
+      <c r="I24" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J24" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C24,E24,G24,H24,I24),0)</f>
-        <v>6</v>
-      </c>
-      <c r="K24" s="1" t="str">
-        <f aca="false">IF(J24&gt;7,"TEA",IF(J24&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
-      </c>
-      <c r="XCZ24" s="1"/>
-      <c r="XDA24" s="1"/>
+      <c r="K24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L24" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C24,E24,G24,I24,K24),0)</f>
+        <v>7</v>
+      </c>
+      <c r="M24" s="1" t="str">
+        <f aca="false">IF(L24&gt;6,"TEA",IF(L24&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
+      </c>
       <c r="XDB24" s="1"/>
       <c r="XDC24" s="1"/>
       <c r="XDD24" s="1"/>
@@ -4469,9 +4717,9 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="C25" s="5" t="n">
         <v>7</v>
       </c>
       <c r="D25" s="3" t="n">
@@ -4480,25 +4728,31 @@
       <c r="E25" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F25" s="10" t="n">
+      <c r="F25" s="11" t="n">
         <v>46171</v>
       </c>
-      <c r="G25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="1" t="n">
-        <v>1</v>
+      <c r="G25" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>46171</v>
       </c>
       <c r="I25" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="J25" s="1" t="n">
-        <f aca="false">ROUND(AVERAGE(C25,E25,G25,H25,I25),0)</f>
-        <v>4</v>
-      </c>
-      <c r="K25" s="1" t="str">
-        <f aca="false">IF(J25&gt;7,"TEA",IF(J25&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
+      <c r="J25" s="3" t="n">
+        <v>46171</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="L25" s="1" t="n">
+        <f aca="false">ROUND(AVERAGE(C25,E25,G25,I25,K25),0)</f>
+        <v>7</v>
+      </c>
+      <c r="M25" s="1" t="str">
+        <f aca="false">IF(L25&gt;6,"TEA",IF(L25&gt;3,"TEP","TED"))</f>
+        <v>TEA</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4506,57 +4760,57 @@
       <c r="D27" s="2"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C3:G8 C9:D25 G9:G25 E9:F23">
-    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+  <conditionalFormatting sqref="C3:H8 C9:D25 G9:H25 E9:F23 J7">
+    <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="cellIs" priority="3" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>4</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"TEA"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"TEP"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>"TED"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:K25">
-    <cfRule type="cellIs" priority="8" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+  <conditionalFormatting sqref="I3:M6 K7:M25 I7:I11 J8:J11 I12:J25">
+    <cfRule type="cellIs" priority="8" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="cellIs" priority="9" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>4</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="10" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="cellIs" priority="10" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" priority="11" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"TEA"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="12" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="cellIs" priority="12" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"TEP"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="cellIs" priority="13" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>"TED"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24:F25">
-    <cfRule type="cellIs" priority="14" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="cellIs" priority="14" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>4</formula>
       <formula>6</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="15" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="cellIs" priority="15" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>4</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="16" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="cellIs" priority="16" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>6</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4592,7 +4846,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>10</v>
@@ -4600,7 +4854,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>9</v>
@@ -4608,7 +4862,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>9</v>
@@ -4616,7 +4870,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>9</v>
@@ -4624,7 +4878,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C6" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>10</v>
@@ -4632,7 +4886,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C7" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>9</v>
@@ -4640,7 +4894,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>8</v>
@@ -4648,7 +4902,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C9" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>9</v>
@@ -4656,7 +4910,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="1" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>9</v>
@@ -4664,7 +4918,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>8</v>
@@ -4672,7 +4926,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>10</v>
@@ -4680,7 +4934,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>10</v>
@@ -4688,7 +4942,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C14" s="1" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>10</v>
@@ -4746,10 +5000,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>7</v>
@@ -4763,10 +5017,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>10</v>
@@ -4780,7 +5034,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>
@@ -4794,10 +5048,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>6</v>
@@ -4811,7 +5065,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>1</v>
@@ -4825,10 +5079,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>10</v>
@@ -4847,7 +5101,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C8" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>6</v>
@@ -4858,10 +5112,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>10</v>
@@ -4875,7 +5129,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>1</v>
@@ -4889,7 +5143,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>1</v>
@@ -4903,10 +5157,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>10</v>
@@ -4920,10 +5174,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>10</v>
@@ -4937,10 +5191,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>10</v>
@@ -4959,7 +5213,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C15" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>9</v>
@@ -4970,10 +5224,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>10</v>
@@ -4987,10 +5241,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>7</v>
@@ -5004,7 +5258,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>1</v>
@@ -5018,10 +5272,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>9</v>
@@ -5035,10 +5289,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>9</v>
@@ -5052,10 +5306,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>10</v>
@@ -5069,10 +5323,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>8</v>
@@ -5086,7 +5340,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>1</v>
@@ -5100,10 +5354,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>10</v>
@@ -5117,10 +5371,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>5</v>
@@ -5134,7 +5388,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>1</v>
@@ -5197,10 +5451,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>10</v>
@@ -5214,10 +5468,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>10</v>
@@ -5231,7 +5485,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>
@@ -5245,10 +5499,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>8</v>
@@ -5262,10 +5516,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>10</v>
@@ -5279,10 +5533,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>10</v>
@@ -5296,7 +5550,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>1</v>
@@ -5310,10 +5564,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>8</v>
@@ -5327,7 +5581,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>1</v>
@@ -5341,7 +5595,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>1</v>
@@ -5355,10 +5609,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>10</v>
@@ -5372,10 +5626,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>10</v>
@@ -5389,10 +5643,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>9</v>
@@ -5406,7 +5660,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>1</v>
@@ -5420,10 +5674,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>10</v>
@@ -5437,10 +5691,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>9</v>
@@ -5454,10 +5708,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>10</v>
@@ -5471,10 +5725,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>8</v>
@@ -5488,7 +5742,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>1</v>
@@ -5502,7 +5756,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>1</v>
@@ -5516,10 +5770,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>9</v>
@@ -5533,10 +5787,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>10</v>
@@ -5555,7 +5809,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>6</v>
@@ -5566,7 +5820,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>1</v>
@@ -5645,10 +5899,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>4</v>
@@ -5662,10 +5916,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>9</v>
@@ -5679,7 +5933,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>1</v>
@@ -5693,7 +5947,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>1</v>
@@ -5707,7 +5961,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>1</v>
@@ -5721,10 +5975,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>9</v>
@@ -5738,7 +5992,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>1</v>
@@ -5752,7 +6006,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>1</v>
@@ -5766,7 +6020,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>1</v>
@@ -5780,7 +6034,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>1</v>
@@ -5794,10 +6048,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>9</v>
@@ -5811,10 +6065,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>10</v>
@@ -5828,10 +6082,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>5</v>
@@ -5845,10 +6099,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>1</v>
@@ -5862,10 +6116,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D16" s="1" t="n">
         <v>10</v>
@@ -5879,10 +6133,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>9</v>
@@ -5896,10 +6150,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="D18" s="1" t="n">
         <v>10</v>
@@ -5913,10 +6167,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>7</v>
@@ -5930,7 +6184,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>77</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>1</v>
@@ -5944,7 +6198,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>1</v>
@@ -5958,10 +6212,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="D22" s="1" t="n">
         <v>10</v>
@@ -5975,10 +6229,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D23" s="1" t="n">
         <v>10</v>
@@ -5997,7 +6251,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C24" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>6</v>
@@ -6005,7 +6259,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>1</v>
@@ -6016,7 +6270,7 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>1</v>

--- a/inasistencias-5a-TecnicasDigitales/alumnos-5a-TecnicasDigitales.xlsx
+++ b/inasistencias-5a-TecnicasDigitales/alumnos-5a-TecnicasDigitales.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="106">
   <si>
     <t xml:space="preserve">armar grupos y arrancar proyecto</t>
   </si>
@@ -427,7 +427,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -469,6 +469,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -712,9 +716,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.07"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="35.71"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="26" min="5" style="1" width="8.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="986" min="986" style="1" width="9.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16348" min="16347" style="1" width="10.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16352" min="16349" style="0" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="985" min="985" style="1" width="9.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16351" min="16346" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16352" min="16352" style="0" width="10.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16353" style="1" width="10.58"/>
   </cols>
   <sheetData>
@@ -821,65 +825,63 @@
         <v>5</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>46248</v>
-      </c>
-      <c r="AG2" s="3" t="n">
         <v>46255</v>
       </c>
+      <c r="AG2" s="3" t="s">
+        <v>5</v>
+      </c>
       <c r="AH2" s="3" t="n">
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="AJ2" s="3" t="n">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="AQ2" s="3" t="n">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="AR2" s="3" t="n">
-        <v>46332</v>
+        <v>46339</v>
       </c>
       <c r="AS2" s="3" t="n">
-        <v>46339</v>
+        <v>46346</v>
       </c>
       <c r="AT2" s="3" t="n">
-        <v>46346</v>
+        <v>46353</v>
       </c>
       <c r="AU2" s="3" t="n">
-        <v>46353</v>
+        <v>46360</v>
       </c>
       <c r="AV2" s="3" t="n">
-        <v>46360</v>
+        <v>46367</v>
       </c>
       <c r="AW2" s="3" t="n">
-        <v>46367</v>
+        <v>46374</v>
       </c>
       <c r="AX2" s="3" t="n">
-        <v>46374</v>
-      </c>
-      <c r="AY2" s="3" t="n">
         <v>46381</v>
       </c>
+      <c r="AY2" s="3"/>
       <c r="AZ2" s="3"/>
       <c r="BA2" s="3"/>
       <c r="BB2" s="3"/>
@@ -927,7 +929,6 @@
       <c r="CR2" s="3"/>
       <c r="CS2" s="3"/>
       <c r="CT2" s="3"/>
-      <c r="CU2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -1015,8 +1016,11 @@
       <c r="AC3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AD3" s="6" t="s">
-        <v>16</v>
+      <c r="AD3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF3" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1102,7 +1106,10 @@
       <c r="AC4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AD4" s="6" t="s">
+      <c r="AD4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF4" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1191,12 +1198,16 @@
       <c r="AD5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="AKX5" s="7"/>
+      <c r="AF5" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AKW5" s="7"/>
+      <c r="XDR5" s="7"/>
       <c r="XDS5" s="7"/>
-      <c r="XDT5" s="7"/>
-      <c r="XDU5" s="0"/>
-      <c r="XDV5" s="0"/>
-      <c r="XDW5" s="0"/>
+      <c r="XDT5" s="1"/>
+      <c r="XDU5" s="1"/>
+      <c r="XDV5" s="1"/>
+      <c r="XDW5" s="1"/>
       <c r="XDX5" s="0"/>
       <c r="XDY5" s="7"/>
       <c r="XDZ5" s="7"/>
@@ -1314,7 +1325,10 @@
       <c r="AC6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AD6" s="6" t="s">
+      <c r="AD6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF6" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1403,7 +1417,10 @@
       <c r="AC7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AD7" s="6" t="s">
+      <c r="AD7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF7" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1490,7 +1507,10 @@
       <c r="AC8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AD8" s="6" t="s">
+      <c r="AD8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF8" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1580,7 +1600,10 @@
       <c r="AC9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AD9" s="6" t="s">
+      <c r="AD9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF9" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1667,7 +1690,10 @@
       <c r="AC10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AD10" s="6" t="s">
+      <c r="AD10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF10" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1756,12 +1782,16 @@
       <c r="AD11" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="AKX11" s="7"/>
+      <c r="AF11" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AKW11" s="7"/>
+      <c r="XDR11" s="7"/>
       <c r="XDS11" s="7"/>
-      <c r="XDT11" s="7"/>
-      <c r="XDU11" s="0"/>
-      <c r="XDV11" s="0"/>
-      <c r="XDW11" s="0"/>
+      <c r="XDT11" s="1"/>
+      <c r="XDU11" s="1"/>
+      <c r="XDV11" s="1"/>
+      <c r="XDW11" s="1"/>
       <c r="XDX11" s="0"/>
       <c r="XDY11" s="7"/>
       <c r="XDZ11" s="7"/>
@@ -1882,7 +1912,10 @@
       <c r="AC12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AD12" s="6" t="s">
+      <c r="AD12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF12" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1969,8 +2002,11 @@
       <c r="AC13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AD13" s="6" t="s">
-        <v>16</v>
+      <c r="AD13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF13" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2059,8 +2095,11 @@
       <c r="AC14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AD14" s="6" t="s">
-        <v>17</v>
+      <c r="AD14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF14" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2151,6 +2190,10 @@
       <c r="AE15" s="10" t="n">
         <v>0.541666666666667</v>
       </c>
+      <c r="AF15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AKW15" s="1"/>
       <c r="AKX15" s="1"/>
       <c r="AKY15" s="1"/>
       <c r="AKZ15" s="1"/>
@@ -2195,12 +2238,12 @@
       <c r="AMM15" s="1"/>
       <c r="AMN15" s="1"/>
       <c r="AMO15" s="1"/>
-      <c r="AMP15" s="1"/>
+      <c r="XDR15" s="1"/>
       <c r="XDS15" s="1"/>
       <c r="XDT15" s="1"/>
-      <c r="XDU15" s="0"/>
-      <c r="XDV15" s="0"/>
-      <c r="XDW15" s="0"/>
+      <c r="XDU15" s="1"/>
+      <c r="XDV15" s="1"/>
+      <c r="XDW15" s="1"/>
       <c r="XDX15" s="0"/>
     </row>
     <row r="16" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2288,9 +2331,12 @@
       <c r="AD16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="XDU16" s="0"/>
-      <c r="XDV16" s="0"/>
-      <c r="XDW16" s="0"/>
+      <c r="AF16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG16" s="4" t="n">
+        <v>0.534722222222222</v>
+      </c>
       <c r="XDX16" s="0"/>
     </row>
     <row r="17" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2378,9 +2424,9 @@
       <c r="AD17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="XDU17" s="0"/>
-      <c r="XDV17" s="0"/>
-      <c r="XDW17" s="0"/>
+      <c r="AF17" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="XDX17" s="0"/>
     </row>
     <row r="18" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2468,6 +2514,10 @@
       <c r="AD18" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="AF18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AKW18" s="1"/>
       <c r="AKX18" s="1"/>
       <c r="AKY18" s="1"/>
       <c r="AKZ18" s="1"/>
@@ -2512,12 +2562,12 @@
       <c r="AMM18" s="1"/>
       <c r="AMN18" s="1"/>
       <c r="AMO18" s="1"/>
-      <c r="AMP18" s="1"/>
+      <c r="XDR18" s="1"/>
       <c r="XDS18" s="1"/>
       <c r="XDT18" s="1"/>
-      <c r="XDU18" s="0"/>
-      <c r="XDV18" s="0"/>
-      <c r="XDW18" s="0"/>
+      <c r="XDU18" s="1"/>
+      <c r="XDV18" s="1"/>
+      <c r="XDW18" s="1"/>
       <c r="XDX18" s="0"/>
     </row>
     <row r="19" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2605,6 +2655,10 @@
       <c r="AD19" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="AF19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AKW19" s="1"/>
       <c r="AKX19" s="1"/>
       <c r="AKY19" s="1"/>
       <c r="AKZ19" s="1"/>
@@ -2649,12 +2703,12 @@
       <c r="AMM19" s="1"/>
       <c r="AMN19" s="1"/>
       <c r="AMO19" s="1"/>
-      <c r="AMP19" s="1"/>
+      <c r="XDR19" s="1"/>
       <c r="XDS19" s="1"/>
       <c r="XDT19" s="1"/>
-      <c r="XDU19" s="0"/>
-      <c r="XDV19" s="0"/>
-      <c r="XDW19" s="0"/>
+      <c r="XDU19" s="1"/>
+      <c r="XDV19" s="1"/>
+      <c r="XDW19" s="1"/>
       <c r="XDX19" s="0"/>
     </row>
     <row r="20" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2742,9 +2796,9 @@
       <c r="AD20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="XDU20" s="0"/>
-      <c r="XDV20" s="0"/>
-      <c r="XDW20" s="0"/>
+      <c r="AF20" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="XDX20" s="0"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2833,8 +2887,11 @@
       <c r="AC21" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AD21" s="6" t="s">
-        <v>16</v>
+      <c r="AD21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF21" s="6" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="22" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2922,12 +2979,16 @@
       <c r="AD22" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="AKX22" s="7"/>
+      <c r="AF22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="AKW22" s="7"/>
+      <c r="XDR22" s="7"/>
       <c r="XDS22" s="7"/>
-      <c r="XDT22" s="7"/>
-      <c r="XDU22" s="0"/>
-      <c r="XDV22" s="0"/>
-      <c r="XDW22" s="0"/>
+      <c r="XDT22" s="1"/>
+      <c r="XDU22" s="1"/>
+      <c r="XDV22" s="1"/>
+      <c r="XDW22" s="1"/>
       <c r="XDX22" s="0"/>
       <c r="XDY22" s="7"/>
       <c r="XDZ22" s="7"/>
@@ -3048,7 +3109,10 @@
       <c r="AC23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AD23" s="6" t="s">
+      <c r="AD23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF23" s="6" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3137,6 +3201,10 @@
       <c r="AD24" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="AF24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AKW24" s="1"/>
       <c r="AKX24" s="1"/>
       <c r="AKY24" s="1"/>
       <c r="AKZ24" s="1"/>
@@ -3181,12 +3249,12 @@
       <c r="AMM24" s="1"/>
       <c r="AMN24" s="1"/>
       <c r="AMO24" s="1"/>
-      <c r="AMP24" s="1"/>
+      <c r="XDR24" s="1"/>
       <c r="XDS24" s="1"/>
       <c r="XDT24" s="1"/>
-      <c r="XDU24" s="0"/>
-      <c r="XDV24" s="0"/>
-      <c r="XDW24" s="0"/>
+      <c r="XDU24" s="1"/>
+      <c r="XDV24" s="1"/>
+      <c r="XDW24" s="1"/>
       <c r="XDX24" s="0"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3275,8 +3343,14 @@
       <c r="AC25" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AD25" s="6" t="s">
-        <v>16</v>
+      <c r="AD25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF25" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AG25" s="11" t="n">
+        <v>0.5625</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3344,6 +3418,10 @@
         <v>16</v>
       </c>
       <c r="AE26" s="1"/>
+      <c r="AF26" s="1" t="n">
+        <f aca="false">COUNTIF(AF3:AF25,"P")</f>
+        <v>13</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="1" t="s">
@@ -3419,6 +3497,10 @@
         <v>0</v>
       </c>
       <c r="AE27" s="2"/>
+      <c r="AF27" s="2" t="n">
+        <f aca="false">COUNTIF(AF3:AF25,"M")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
@@ -3494,6 +3576,10 @@
         <v>1</v>
       </c>
       <c r="AE28" s="2"/>
+      <c r="AF28" s="2" t="n">
+        <f aca="false">COUNTIF(AF3:AF25,"T")</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="1" t="s">
@@ -3569,6 +3655,10 @@
         <v>17</v>
       </c>
       <c r="AE29" s="2"/>
+      <c r="AF29" s="2" t="n">
+        <f aca="false">SUM(AF26:AF28)</f>
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="V3:V25">
@@ -4728,7 +4818,7 @@
       <c r="E25" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="F25" s="12" t="n">
         <v>46171</v>
       </c>
       <c r="G25" s="5" t="n">

--- a/inasistencias-5a-TecnicasDigitales/alumnos-5a-TecnicasDigitales.xlsx
+++ b/inasistencias-5a-TecnicasDigitales/alumnos-5a-TecnicasDigitales.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="112">
   <si>
     <t xml:space="preserve">armar grupos y arrancar proyecto</t>
   </si>
@@ -325,6 +325,24 @@
   </si>
   <si>
     <t xml:space="preserve">valoracion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grupo </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avance 28-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acance 4/8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avance 18/9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avance 25/9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avance 2/10</t>
   </si>
   <si>
     <t xml:space="preserve">apellido</t>
@@ -456,6 +474,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -469,10 +491,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -716,10 +734,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.07"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="4" min="4" style="1" width="35.71"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="26" min="5" style="1" width="8.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="985" min="985" style="1" width="9.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16351" min="16346" style="1" width="10.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16352" min="16352" style="0" width="10.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16353" style="1" width="10.58"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="38" min="27" style="0" width="8.86"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="41" min="41" style="0" width="8.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="988" min="988" style="1" width="9.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16349" style="1" width="10.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -831,59 +849,65 @@
         <v>5</v>
       </c>
       <c r="AH2" s="3" t="n">
+        <v>46262</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ2" s="3" t="n">
         <v>46269</v>
       </c>
-      <c r="AI2" s="3" t="n">
-        <v>46276</v>
-      </c>
-      <c r="AJ2" s="3" t="n">
+      <c r="AK2" s="3" t="n">
         <v>46283</v>
       </c>
-      <c r="AK2" s="3" t="n">
+      <c r="AL2" s="3" t="n">
         <v>46290</v>
       </c>
-      <c r="AL2" s="3" t="n">
+      <c r="AM2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN2" s="3" t="n">
         <v>46297</v>
       </c>
-      <c r="AM2" s="3" t="n">
+      <c r="AO2" s="3" t="n">
         <v>46304</v>
       </c>
-      <c r="AN2" s="3" t="n">
+      <c r="AP2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AQ2" s="3" t="n">
         <v>46311</v>
       </c>
-      <c r="AO2" s="3" t="n">
+      <c r="AR2" s="3" t="n">
         <v>46318</v>
       </c>
-      <c r="AP2" s="3" t="n">
+      <c r="AS2" s="3" t="n">
         <v>46325</v>
       </c>
-      <c r="AQ2" s="3" t="n">
+      <c r="AT2" s="3" t="n">
         <v>46332</v>
       </c>
-      <c r="AR2" s="3" t="n">
+      <c r="AU2" s="3" t="n">
         <v>46339</v>
       </c>
-      <c r="AS2" s="3" t="n">
+      <c r="AV2" s="3" t="n">
         <v>46346</v>
       </c>
-      <c r="AT2" s="3" t="n">
+      <c r="AW2" s="3" t="n">
         <v>46353</v>
       </c>
-      <c r="AU2" s="3" t="n">
+      <c r="AX2" s="3" t="n">
         <v>46360</v>
       </c>
-      <c r="AV2" s="3" t="n">
+      <c r="AY2" s="3" t="n">
         <v>46367</v>
       </c>
-      <c r="AW2" s="3" t="n">
+      <c r="AZ2" s="3" t="n">
         <v>46374</v>
       </c>
-      <c r="AX2" s="3" t="n">
+      <c r="BA2" s="3" t="n">
         <v>46381</v>
       </c>
-      <c r="AY2" s="3"/>
-      <c r="AZ2" s="3"/>
-      <c r="BA2" s="3"/>
       <c r="BB2" s="3"/>
       <c r="BC2" s="3"/>
       <c r="BD2" s="3"/>
@@ -929,6 +953,9 @@
       <c r="CR2" s="3"/>
       <c r="CS2" s="3"/>
       <c r="CT2" s="3"/>
+      <c r="CU2" s="3"/>
+      <c r="CV2" s="3"/>
+      <c r="CW2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -1019,8 +1046,32 @@
       <c r="AD3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AF3" s="6" t="s">
+      <c r="AF3" s="2" t="s">
         <v>19</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AI3" s="4" t="n">
+        <v>0.555555555555556</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM3" s="4" t="n">
+        <v>0.548611111111111</v>
+      </c>
+      <c r="AN3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AP3" s="7" t="n">
+        <v>0.541666666666667</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1109,51 +1160,66 @@
       <c r="AD4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AF4" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
+      <c r="AF4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN4" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="8" t="s">
+      <c r="E5" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="M5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="P5" s="8" t="s">
+      <c r="I5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P5" s="9" t="s">
         <v>17</v>
       </c>
       <c r="Q5" s="1" t="n">
@@ -1180,67 +1246,79 @@
         <f aca="false">ROUND((Q5+R5/2+S5/4)*10/U5,0)</f>
         <v>1</v>
       </c>
-      <c r="W5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="X5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA5" s="8" t="s">
+      <c r="W5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="X5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="AB5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AD5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AKW5" s="7"/>
-      <c r="XDR5" s="7"/>
-      <c r="XDS5" s="7"/>
-      <c r="XDT5" s="1"/>
-      <c r="XDU5" s="1"/>
-      <c r="XDV5" s="1"/>
+      <c r="AB5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN5" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AKZ5" s="8"/>
+      <c r="XDU5" s="8"/>
+      <c r="XDV5" s="8"/>
       <c r="XDW5" s="1"/>
-      <c r="XDX5" s="0"/>
-      <c r="XDY5" s="7"/>
-      <c r="XDZ5" s="7"/>
-      <c r="XEA5" s="7"/>
-      <c r="XEB5" s="7"/>
-      <c r="XEC5" s="7"/>
-      <c r="XED5" s="7"/>
-      <c r="XEE5" s="7"/>
-      <c r="XEF5" s="7"/>
-      <c r="XEG5" s="7"/>
-      <c r="XEH5" s="7"/>
-      <c r="XEI5" s="7"/>
-      <c r="XEJ5" s="7"/>
-      <c r="XEK5" s="7"/>
-      <c r="XEL5" s="7"/>
-      <c r="XEM5" s="7"/>
-      <c r="XEN5" s="7"/>
-      <c r="XEO5" s="7"/>
-      <c r="XEP5" s="7"/>
-      <c r="XEQ5" s="7"/>
-      <c r="XER5" s="7"/>
-      <c r="XES5" s="7"/>
-      <c r="XET5" s="7"/>
-      <c r="XEU5" s="7"/>
-      <c r="XEV5" s="7"/>
-      <c r="XEW5" s="7"/>
-      <c r="XEX5" s="7"/>
-      <c r="XEY5" s="7"/>
-      <c r="XEZ5" s="7"/>
-      <c r="XFA5" s="7"/>
-      <c r="XFB5" s="7"/>
-      <c r="XFC5" s="7"/>
-      <c r="XFD5" s="7"/>
+      <c r="XDX5" s="1"/>
+      <c r="XDY5" s="1"/>
+      <c r="XDZ5" s="1"/>
+      <c r="XEA5" s="1"/>
+      <c r="XEB5" s="8"/>
+      <c r="XEC5" s="8"/>
+      <c r="XED5" s="8"/>
+      <c r="XEE5" s="8"/>
+      <c r="XEF5" s="8"/>
+      <c r="XEG5" s="8"/>
+      <c r="XEH5" s="8"/>
+      <c r="XEI5" s="8"/>
+      <c r="XEJ5" s="8"/>
+      <c r="XEK5" s="8"/>
+      <c r="XEL5" s="8"/>
+      <c r="XEM5" s="8"/>
+      <c r="XEN5" s="8"/>
+      <c r="XEO5" s="8"/>
+      <c r="XEP5" s="8"/>
+      <c r="XEQ5" s="8"/>
+      <c r="XER5" s="8"/>
+      <c r="XES5" s="8"/>
+      <c r="XET5" s="8"/>
+      <c r="XEU5" s="8"/>
+      <c r="XEV5" s="8"/>
+      <c r="XEW5" s="8"/>
+      <c r="XEX5" s="8"/>
+      <c r="XEY5" s="8"/>
+      <c r="XEZ5" s="8"/>
+      <c r="XFA5" s="8"/>
+      <c r="XFB5" s="8"/>
+      <c r="XFC5" s="8"/>
+      <c r="XFD5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -1328,7 +1406,22 @@
       <c r="AD6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AF6" s="6" t="s">
+      <c r="AF6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN6" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1420,7 +1513,22 @@
       <c r="AD7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AF7" s="6" t="s">
+      <c r="AF7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN7" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1510,7 +1618,22 @@
       <c r="AD8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AF8" s="6" t="s">
+      <c r="AF8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN8" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1603,8 +1726,23 @@
       <c r="AD9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AF9" s="6" t="s">
-        <v>17</v>
+      <c r="AF9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN9" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1693,138 +1831,165 @@
       <c r="AD10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AF10" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="7" t="s">
+      <c r="AF10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN10" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="8" t="s">
+      <c r="E11" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I11" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="N11" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="P11" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q11" s="8" t="n">
+      <c r="I11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="N11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q11" s="9" t="n">
         <f aca="false">COUNTIF(E11:P11,"P")</f>
         <v>1</v>
       </c>
-      <c r="R11" s="8" t="n">
+      <c r="R11" s="9" t="n">
         <f aca="false">COUNTIF(E11:P11,"M")</f>
         <v>0</v>
       </c>
-      <c r="S11" s="8" t="n">
+      <c r="S11" s="9" t="n">
         <f aca="false">COUNTIF(E11:P11,"T")</f>
         <v>0</v>
       </c>
-      <c r="T11" s="8" t="n">
+      <c r="T11" s="9" t="n">
         <f aca="false">COUNTIF(E11:P11,"A")</f>
         <v>8</v>
       </c>
-      <c r="U11" s="8" t="n">
+      <c r="U11" s="9" t="n">
         <f aca="false">SUM(Q11:T11)</f>
         <v>9</v>
       </c>
-      <c r="V11" s="9" t="n">
+      <c r="V11" s="10" t="n">
         <f aca="false">ROUND((Q11+R11/2+S11/4)*10/U11,0)</f>
         <v>1</v>
       </c>
-      <c r="W11" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="X11" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA11" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB11" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC11" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AD11" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF11" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AKW11" s="7"/>
-      <c r="XDR11" s="7"/>
-      <c r="XDS11" s="7"/>
-      <c r="XDT11" s="1"/>
-      <c r="XDU11" s="1"/>
-      <c r="XDV11" s="1"/>
+      <c r="W11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="X11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN11" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AKZ11" s="8"/>
+      <c r="XDU11" s="8"/>
+      <c r="XDV11" s="8"/>
       <c r="XDW11" s="1"/>
-      <c r="XDX11" s="0"/>
-      <c r="XDY11" s="7"/>
-      <c r="XDZ11" s="7"/>
-      <c r="XEA11" s="7"/>
-      <c r="XEB11" s="7"/>
-      <c r="XEC11" s="7"/>
-      <c r="XED11" s="7"/>
-      <c r="XEE11" s="7"/>
-      <c r="XEF11" s="7"/>
-      <c r="XEG11" s="7"/>
-      <c r="XEH11" s="7"/>
-      <c r="XEI11" s="7"/>
-      <c r="XEJ11" s="7"/>
-      <c r="XEK11" s="7"/>
-      <c r="XEL11" s="7"/>
-      <c r="XEM11" s="7"/>
-      <c r="XEN11" s="7"/>
-      <c r="XEO11" s="7"/>
-      <c r="XEP11" s="7"/>
-      <c r="XEQ11" s="7"/>
-      <c r="XER11" s="7"/>
-      <c r="XES11" s="7"/>
-      <c r="XET11" s="7"/>
-      <c r="XEU11" s="7"/>
-      <c r="XEV11" s="7"/>
-      <c r="XEW11" s="7"/>
-      <c r="XEX11" s="7"/>
-      <c r="XEY11" s="7"/>
-      <c r="XEZ11" s="7"/>
-      <c r="XFA11" s="7"/>
-      <c r="XFB11" s="7"/>
-      <c r="XFC11" s="7"/>
-      <c r="XFD11" s="7"/>
+      <c r="XDX11" s="1"/>
+      <c r="XDY11" s="1"/>
+      <c r="XDZ11" s="1"/>
+      <c r="XEA11" s="1"/>
+      <c r="XEB11" s="8"/>
+      <c r="XEC11" s="8"/>
+      <c r="XED11" s="8"/>
+      <c r="XEE11" s="8"/>
+      <c r="XEF11" s="8"/>
+      <c r="XEG11" s="8"/>
+      <c r="XEH11" s="8"/>
+      <c r="XEI11" s="8"/>
+      <c r="XEJ11" s="8"/>
+      <c r="XEK11" s="8"/>
+      <c r="XEL11" s="8"/>
+      <c r="XEM11" s="8"/>
+      <c r="XEN11" s="8"/>
+      <c r="XEO11" s="8"/>
+      <c r="XEP11" s="8"/>
+      <c r="XEQ11" s="8"/>
+      <c r="XER11" s="8"/>
+      <c r="XES11" s="8"/>
+      <c r="XET11" s="8"/>
+      <c r="XEU11" s="8"/>
+      <c r="XEV11" s="8"/>
+      <c r="XEW11" s="8"/>
+      <c r="XEX11" s="8"/>
+      <c r="XEY11" s="8"/>
+      <c r="XEZ11" s="8"/>
+      <c r="XFA11" s="8"/>
+      <c r="XFB11" s="8"/>
+      <c r="XFC11" s="8"/>
+      <c r="XFD11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
@@ -1915,7 +2080,22 @@
       <c r="AD12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AF12" s="6" t="s">
+      <c r="AF12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN12" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2005,8 +2185,26 @@
       <c r="AD13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AF13" s="6" t="s">
-        <v>17</v>
+      <c r="AF13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM13" s="4" t="n">
+        <v>0.548611111111111</v>
+      </c>
+      <c r="AN13" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2098,8 +2296,26 @@
       <c r="AD14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AF14" s="6" t="s">
-        <v>16</v>
+      <c r="AF14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN14" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AP14" s="7" t="n">
+        <v>0.5625</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2187,15 +2403,27 @@
       <c r="AD15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AE15" s="10" t="n">
+      <c r="AE15" s="11" t="n">
         <v>0.541666666666667</v>
       </c>
       <c r="AF15" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AKW15" s="1"/>
-      <c r="AKX15" s="1"/>
-      <c r="AKY15" s="1"/>
+      <c r="AH15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN15" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="AKZ15" s="1"/>
       <c r="ALA15" s="1"/>
       <c r="ALB15" s="1"/>
@@ -2238,13 +2466,16 @@
       <c r="AMM15" s="1"/>
       <c r="AMN15" s="1"/>
       <c r="AMO15" s="1"/>
-      <c r="XDR15" s="1"/>
-      <c r="XDS15" s="1"/>
-      <c r="XDT15" s="1"/>
+      <c r="AMP15" s="1"/>
+      <c r="AMQ15" s="1"/>
+      <c r="AMR15" s="1"/>
       <c r="XDU15" s="1"/>
       <c r="XDV15" s="1"/>
       <c r="XDW15" s="1"/>
-      <c r="XDX15" s="0"/>
+      <c r="XDX15" s="1"/>
+      <c r="XDY15" s="1"/>
+      <c r="XDZ15" s="1"/>
+      <c r="XEA15" s="1"/>
     </row>
     <row r="16" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
@@ -2337,7 +2568,21 @@
       <c r="AG16" s="4" t="n">
         <v>0.534722222222222</v>
       </c>
-      <c r="XDX16" s="0"/>
+      <c r="AH16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN16" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="17" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
@@ -2427,7 +2672,21 @@
       <c r="AF17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="XDX17" s="0"/>
+      <c r="AH17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN17" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="18" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
@@ -2517,9 +2776,21 @@
       <c r="AF18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AKW18" s="1"/>
-      <c r="AKX18" s="1"/>
-      <c r="AKY18" s="1"/>
+      <c r="AH18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN18" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="AKZ18" s="1"/>
       <c r="ALA18" s="1"/>
       <c r="ALB18" s="1"/>
@@ -2562,13 +2833,16 @@
       <c r="AMM18" s="1"/>
       <c r="AMN18" s="1"/>
       <c r="AMO18" s="1"/>
-      <c r="XDR18" s="1"/>
-      <c r="XDS18" s="1"/>
-      <c r="XDT18" s="1"/>
+      <c r="AMP18" s="1"/>
+      <c r="AMQ18" s="1"/>
+      <c r="AMR18" s="1"/>
       <c r="XDU18" s="1"/>
       <c r="XDV18" s="1"/>
       <c r="XDW18" s="1"/>
-      <c r="XDX18" s="0"/>
+      <c r="XDX18" s="1"/>
+      <c r="XDY18" s="1"/>
+      <c r="XDZ18" s="1"/>
+      <c r="XEA18" s="1"/>
     </row>
     <row r="19" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
@@ -2658,9 +2932,21 @@
       <c r="AF19" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AKW19" s="1"/>
-      <c r="AKX19" s="1"/>
-      <c r="AKY19" s="1"/>
+      <c r="AH19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN19" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="AKZ19" s="1"/>
       <c r="ALA19" s="1"/>
       <c r="ALB19" s="1"/>
@@ -2703,13 +2989,16 @@
       <c r="AMM19" s="1"/>
       <c r="AMN19" s="1"/>
       <c r="AMO19" s="1"/>
-      <c r="XDR19" s="1"/>
-      <c r="XDS19" s="1"/>
-      <c r="XDT19" s="1"/>
+      <c r="AMP19" s="1"/>
+      <c r="AMQ19" s="1"/>
+      <c r="AMR19" s="1"/>
       <c r="XDU19" s="1"/>
       <c r="XDV19" s="1"/>
       <c r="XDW19" s="1"/>
-      <c r="XDX19" s="0"/>
+      <c r="XDX19" s="1"/>
+      <c r="XDY19" s="1"/>
+      <c r="XDZ19" s="1"/>
+      <c r="XEA19" s="1"/>
     </row>
     <row r="20" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
@@ -2799,7 +3088,21 @@
       <c r="AF20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="XDX20" s="0"/>
+      <c r="AH20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN20" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
@@ -2890,138 +3193,162 @@
       <c r="AD21" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AF21" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="n">
+      <c r="AF21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN21" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" s="9" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E22" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" s="8" t="s">
+      <c r="E22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I22" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="M22" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="N22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="P22" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q22" s="8" t="n">
+      <c r="I22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P22" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q22" s="9" t="n">
         <f aca="false">COUNTIF(E22:P22,"P")</f>
         <v>5</v>
       </c>
-      <c r="R22" s="8" t="n">
+      <c r="R22" s="9" t="n">
         <f aca="false">COUNTIF(E22:P22,"M")</f>
         <v>0</v>
       </c>
-      <c r="S22" s="8" t="n">
+      <c r="S22" s="9" t="n">
         <f aca="false">COUNTIF(E22:P22,"T")</f>
         <v>0</v>
       </c>
-      <c r="T22" s="8" t="n">
+      <c r="T22" s="9" t="n">
         <f aca="false">COUNTIF(E22:P22,"A")</f>
         <v>4</v>
       </c>
-      <c r="U22" s="8" t="n">
+      <c r="U22" s="9" t="n">
         <f aca="false">SUM(Q22:T22)</f>
         <v>9</v>
       </c>
-      <c r="V22" s="9" t="n">
+      <c r="V22" s="10" t="n">
         <f aca="false">ROUND((Q22+R22/2+S22/4)*10/U22,0)</f>
         <v>6</v>
       </c>
-      <c r="W22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="X22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AB22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AD22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="AKW22" s="7"/>
-      <c r="XDR22" s="7"/>
-      <c r="XDS22" s="7"/>
-      <c r="XDT22" s="1"/>
-      <c r="XDU22" s="1"/>
-      <c r="XDV22" s="1"/>
+      <c r="W22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="X22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN22" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="AKZ22" s="8"/>
+      <c r="XDU22" s="8"/>
+      <c r="XDV22" s="8"/>
       <c r="XDW22" s="1"/>
-      <c r="XDX22" s="0"/>
-      <c r="XDY22" s="7"/>
-      <c r="XDZ22" s="7"/>
-      <c r="XEA22" s="7"/>
-      <c r="XEB22" s="7"/>
-      <c r="XEC22" s="7"/>
-      <c r="XED22" s="7"/>
-      <c r="XEE22" s="7"/>
-      <c r="XEF22" s="7"/>
-      <c r="XEG22" s="7"/>
-      <c r="XEH22" s="7"/>
-      <c r="XEI22" s="7"/>
-      <c r="XEJ22" s="7"/>
-      <c r="XEK22" s="7"/>
-      <c r="XEL22" s="7"/>
-      <c r="XEM22" s="7"/>
-      <c r="XEN22" s="7"/>
-      <c r="XEO22" s="7"/>
-      <c r="XEP22" s="7"/>
-      <c r="XEQ22" s="7"/>
-      <c r="XER22" s="7"/>
-      <c r="XES22" s="7"/>
-      <c r="XET22" s="7"/>
-      <c r="XEU22" s="7"/>
-      <c r="XEV22" s="7"/>
-      <c r="XEW22" s="7"/>
-      <c r="XEX22" s="7"/>
-      <c r="XEY22" s="7"/>
-      <c r="XEZ22" s="7"/>
-      <c r="XFA22" s="7"/>
-      <c r="XFB22" s="7"/>
-      <c r="XFC22" s="7"/>
-      <c r="XFD22" s="7"/>
+      <c r="XDX22" s="1"/>
+      <c r="XDY22" s="1"/>
+      <c r="XDZ22" s="1"/>
+      <c r="XEA22" s="1"/>
+      <c r="XEB22" s="8"/>
+      <c r="XEC22" s="8"/>
+      <c r="XED22" s="8"/>
+      <c r="XEE22" s="8"/>
+      <c r="XEF22" s="8"/>
+      <c r="XEG22" s="8"/>
+      <c r="XEH22" s="8"/>
+      <c r="XEI22" s="8"/>
+      <c r="XEJ22" s="8"/>
+      <c r="XEK22" s="8"/>
+      <c r="XEL22" s="8"/>
+      <c r="XEM22" s="8"/>
+      <c r="XEN22" s="8"/>
+      <c r="XEO22" s="8"/>
+      <c r="XEP22" s="8"/>
+      <c r="XEQ22" s="8"/>
+      <c r="XER22" s="8"/>
+      <c r="XES22" s="8"/>
+      <c r="XET22" s="8"/>
+      <c r="XEU22" s="8"/>
+      <c r="XEV22" s="8"/>
+      <c r="XEW22" s="8"/>
+      <c r="XEX22" s="8"/>
+      <c r="XEY22" s="8"/>
+      <c r="XEZ22" s="8"/>
+      <c r="XFA22" s="8"/>
+      <c r="XFB22" s="8"/>
+      <c r="XFC22" s="8"/>
+      <c r="XFD22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
@@ -3112,8 +3439,23 @@
       <c r="AD23" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AF23" s="6" t="s">
-        <v>17</v>
+      <c r="AF23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN23" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AP23" s="7" t="n">
+        <v>0.541666666666667</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3204,9 +3546,18 @@
       <c r="AF24" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AKW24" s="1"/>
-      <c r="AKX24" s="1"/>
-      <c r="AKY24" s="1"/>
+      <c r="AH24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN24" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="AKZ24" s="1"/>
       <c r="ALA24" s="1"/>
       <c r="ALB24" s="1"/>
@@ -3249,13 +3600,16 @@
       <c r="AMM24" s="1"/>
       <c r="AMN24" s="1"/>
       <c r="AMO24" s="1"/>
-      <c r="XDR24" s="1"/>
-      <c r="XDS24" s="1"/>
-      <c r="XDT24" s="1"/>
+      <c r="AMP24" s="1"/>
+      <c r="AMQ24" s="1"/>
+      <c r="AMR24" s="1"/>
       <c r="XDU24" s="1"/>
       <c r="XDV24" s="1"/>
       <c r="XDW24" s="1"/>
-      <c r="XDX24" s="0"/>
+      <c r="XDX24" s="1"/>
+      <c r="XDY24" s="1"/>
+      <c r="XDZ24" s="1"/>
+      <c r="XEA24" s="1"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
@@ -3346,11 +3700,26 @@
       <c r="AD25" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AF25" s="6" t="s">
+      <c r="AF25" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="AG25" s="11" t="n">
+      <c r="AG25" s="4" t="n">
         <v>0.5625</v>
+      </c>
+      <c r="AH25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM25" s="4" t="n">
+        <v>0.548611111111111</v>
+      </c>
+      <c r="AN25" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3421,6 +3790,24 @@
       <c r="AF26" s="1" t="n">
         <f aca="false">COUNTIF(AF3:AF25,"P")</f>
         <v>13</v>
+      </c>
+      <c r="AH26" s="1" t="n">
+        <f aca="false">COUNTIF(AH3:AH25,"P")</f>
+        <v>15</v>
+      </c>
+      <c r="AI26" s="1"/>
+      <c r="AJ26" s="1" t="n">
+        <f aca="false">COUNTIF(AJ3:AJ25,"P")</f>
+        <v>17</v>
+      </c>
+      <c r="AL26" s="1" t="n">
+        <f aca="false">COUNTIF(AL3:AL25,"P")</f>
+        <v>14</v>
+      </c>
+      <c r="AM26" s="1"/>
+      <c r="AN26" s="1" t="n">
+        <f aca="false">COUNTIF(AN3:AN25,"P")</f>
+        <v>17</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3501,6 +3888,24 @@
         <f aca="false">COUNTIF(AF3:AF25,"M")</f>
         <v>0</v>
       </c>
+      <c r="AH27" s="2" t="n">
+        <f aca="false">COUNTIF(AH3:AH25,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2" t="n">
+        <f aca="false">COUNTIF(AJ3:AJ25,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AL27" s="2" t="n">
+        <f aca="false">COUNTIF(AL3:AL25,"M")</f>
+        <v>0</v>
+      </c>
+      <c r="AM27" s="2"/>
+      <c r="AN27" s="2" t="n">
+        <f aca="false">COUNTIF(AN3:AN25,"M")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
@@ -3578,6 +3983,24 @@
       <c r="AE28" s="2"/>
       <c r="AF28" s="2" t="n">
         <f aca="false">COUNTIF(AF3:AF25,"T")</f>
+        <v>3</v>
+      </c>
+      <c r="AH28" s="2" t="n">
+        <f aca="false">COUNTIF(AH3:AH25,"T")</f>
+        <v>1</v>
+      </c>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2" t="n">
+        <f aca="false">COUNTIF(AJ3:AJ25,"T")</f>
+        <v>0</v>
+      </c>
+      <c r="AL28" s="2" t="n">
+        <f aca="false">COUNTIF(AL3:AL25,"T")</f>
+        <v>3</v>
+      </c>
+      <c r="AM28" s="2"/>
+      <c r="AN28" s="2" t="n">
+        <f aca="false">COUNTIF(AN3:AN25,"T")</f>
         <v>3</v>
       </c>
     </row>
@@ -3658,6 +4081,24 @@
       <c r="AF29" s="2" t="n">
         <f aca="false">SUM(AF26:AF28)</f>
         <v>16</v>
+      </c>
+      <c r="AH29" s="2" t="n">
+        <f aca="false">SUM(AH26:AH28)</f>
+        <v>16</v>
+      </c>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2" t="n">
+        <f aca="false">SUM(AJ26:AJ28)</f>
+        <v>17</v>
+      </c>
+      <c r="AL29" s="2" t="n">
+        <f aca="false">SUM(AL26:AL28)</f>
+        <v>17</v>
+      </c>
+      <c r="AM29" s="2"/>
+      <c r="AN29" s="2" t="n">
+        <f aca="false">SUM(AN26:AN28)</f>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -3693,8 +4134,8 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.36"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="9.66"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="3" min="3" style="1" width="9.36"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="12" min="4" style="1" width="9.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16332" style="1" width="10.58"/>
   </cols>
   <sheetData>
@@ -3735,55 +4176,95 @@
       <c r="M2" s="2" t="s">
         <v>99</v>
       </c>
+      <c r="N2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F3" s="5"/>
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>46171</v>
+      </c>
       <c r="G3" s="5" t="n">
         <v>10</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="J3" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>46171</v>
+      </c>
       <c r="K3" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L3" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C3,E3,G3,I3,K3),0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3" s="1" t="str">
         <f aca="false">IF(L3&gt;6,"TEA",IF(L3&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="R3" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="S3" s="0" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="n">
@@ -3793,167 +4274,220 @@
       <c r="I4" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="J4" s="1"/>
       <c r="K4" s="1" t="n">
         <v>10</v>
       </c>
       <c r="L4" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C4,E4,G4,I4,K4),0)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M4" s="1" t="str">
         <f aca="false">IF(L4&gt;6,"TEA",IF(L4&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
-    </row>
-    <row r="5" s="8" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7" t="n">
-        <v>1</v>
+      <c r="N4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="P4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="R4" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="S4" s="0" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" s="9" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="L5" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C5,E5,G5,I5,K5),0)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M5" s="1" t="str">
         <f aca="false">IF(L5&gt;6,"TEA",IF(L5&gt;3,"TEP","TED"))</f>
-        <v>TED</v>
-      </c>
-      <c r="XDD5" s="7"/>
-      <c r="XDE5" s="7"/>
-      <c r="XDF5" s="7"/>
-      <c r="XDG5" s="7"/>
-      <c r="XDH5" s="7"/>
-      <c r="XDI5" s="7"/>
-      <c r="XDJ5" s="7"/>
-      <c r="XDK5" s="7"/>
-      <c r="XDL5" s="7"/>
-      <c r="XDM5" s="7"/>
-      <c r="XDN5" s="7"/>
-      <c r="XDO5" s="7"/>
-      <c r="XDP5" s="7"/>
-      <c r="XDQ5" s="7"/>
-      <c r="XDR5" s="7"/>
-      <c r="XDS5" s="7"/>
-      <c r="XDT5" s="7"/>
-      <c r="XDU5" s="7"/>
-      <c r="XDV5" s="7"/>
-      <c r="XDW5" s="7"/>
-      <c r="XDX5" s="7"/>
-      <c r="XDY5" s="7"/>
-      <c r="XDZ5" s="7"/>
-      <c r="XEA5" s="7"/>
-      <c r="XEB5" s="7"/>
-      <c r="XEC5" s="7"/>
-      <c r="XED5" s="7"/>
-      <c r="XEE5" s="7"/>
-      <c r="XEF5" s="7"/>
-      <c r="XEG5" s="7"/>
-      <c r="XEH5" s="7"/>
-      <c r="XEI5" s="7"/>
-      <c r="XEJ5" s="7"/>
-      <c r="XEK5" s="7"/>
-      <c r="XEL5" s="7"/>
-      <c r="XEM5" s="7"/>
-      <c r="XEN5" s="7"/>
-      <c r="XEO5" s="7"/>
-      <c r="XEP5" s="7"/>
-      <c r="XEQ5" s="7"/>
-      <c r="XER5" s="7"/>
-      <c r="XES5" s="7"/>
-      <c r="XET5" s="7"/>
-      <c r="XEU5" s="7"/>
-      <c r="XEV5" s="7"/>
-      <c r="XEW5" s="7"/>
-      <c r="XEX5" s="7"/>
-      <c r="XEY5" s="7"/>
-      <c r="XEZ5" s="7"/>
-      <c r="XFA5" s="7"/>
-      <c r="XFB5" s="7"/>
-      <c r="XFC5" s="7"/>
-      <c r="XFD5" s="7"/>
+        <v>TEA</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="R5" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="S5" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="XDD5" s="8"/>
+      <c r="XDE5" s="8"/>
+      <c r="XDF5" s="8"/>
+      <c r="XDG5" s="8"/>
+      <c r="XDH5" s="8"/>
+      <c r="XDI5" s="8"/>
+      <c r="XDJ5" s="8"/>
+      <c r="XDK5" s="8"/>
+      <c r="XDL5" s="8"/>
+      <c r="XDM5" s="8"/>
+      <c r="XDN5" s="8"/>
+      <c r="XDO5" s="8"/>
+      <c r="XDP5" s="8"/>
+      <c r="XDQ5" s="8"/>
+      <c r="XDR5" s="8"/>
+      <c r="XDS5" s="8"/>
+      <c r="XDT5" s="8"/>
+      <c r="XDU5" s="8"/>
+      <c r="XDV5" s="8"/>
+      <c r="XDW5" s="8"/>
+      <c r="XDX5" s="8"/>
+      <c r="XDY5" s="8"/>
+      <c r="XDZ5" s="8"/>
+      <c r="XEA5" s="8"/>
+      <c r="XEB5" s="8"/>
+      <c r="XEC5" s="8"/>
+      <c r="XED5" s="8"/>
+      <c r="XEE5" s="8"/>
+      <c r="XEF5" s="8"/>
+      <c r="XEG5" s="8"/>
+      <c r="XEH5" s="8"/>
+      <c r="XEI5" s="8"/>
+      <c r="XEJ5" s="8"/>
+      <c r="XEK5" s="8"/>
+      <c r="XEL5" s="8"/>
+      <c r="XEM5" s="8"/>
+      <c r="XEN5" s="8"/>
+      <c r="XEO5" s="8"/>
+      <c r="XEP5" s="8"/>
+      <c r="XEQ5" s="8"/>
+      <c r="XER5" s="8"/>
+      <c r="XES5" s="8"/>
+      <c r="XET5" s="8"/>
+      <c r="XEU5" s="8"/>
+      <c r="XEV5" s="8"/>
+      <c r="XEW5" s="8"/>
+      <c r="XEX5" s="8"/>
+      <c r="XEY5" s="8"/>
+      <c r="XEZ5" s="8"/>
+      <c r="XFA5" s="8"/>
+      <c r="XFB5" s="8"/>
+      <c r="XFC5" s="8"/>
+      <c r="XFD5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>46171</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D6" s="5"/>
       <c r="E6" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" s="5"/>
-      <c r="G6" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>46220</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>9</v>
+      <c r="G6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="L6" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C6,E6,G6,I6,K6),0)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M6" s="1" t="str">
         <f aca="false">IF(L6&gt;6,"TEA",IF(L6&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="R6" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="S6" s="0" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>46171</v>
       </c>
+      <c r="E7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>46171</v>
+      </c>
       <c r="G7" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="H7" s="5"/>
+        <v>7</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>46171</v>
+      </c>
       <c r="I7" s="1" t="n">
         <v>7</v>
       </c>
@@ -3961,30 +4495,48 @@
         <v>46171</v>
       </c>
       <c r="K7" s="1" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L7" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C7,E7,G7,I7,K7),0)</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M7" s="1" t="str">
         <f aca="false">IF(L7&gt;6,"TEA",IF(L7&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>9</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="5" t="n">
@@ -3994,18 +4546,35 @@
       <c r="I8" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="J8" s="1"/>
       <c r="K8" s="1" t="n">
         <v>10</v>
       </c>
       <c r="L8" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C8,E8,G8,I8,K8),0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M8" s="1" t="str">
         <f aca="false">IF(L8&gt;6,"TEA",IF(L8&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
@@ -4047,28 +4616,48 @@
         <f aca="false">IF(L9&gt;6,"TEA",IF(L9&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D10" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>46171</v>
+      </c>
       <c r="E10" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>46171</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="H10" s="5"/>
+      <c r="H10" s="3" t="n">
+        <v>46220</v>
+      </c>
       <c r="I10" s="1" t="n">
         <v>7</v>
       </c>
@@ -4076,7 +4665,7 @@
         <v>46220</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L10" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C10,E10,G10,I10,K10),0)</f>
@@ -4086,96 +4675,146 @@
         <f aca="false">IF(L10&gt;6,"TEA",IF(L10&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="5"/>
+        <v>7</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>46171</v>
+      </c>
       <c r="G11" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="1"/>
+        <v>10</v>
+      </c>
       <c r="K11" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L11" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C11,E11,G11,I11,K11),0)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M11" s="1" t="str">
         <f aca="false">IF(L11&gt;6,"TEA",IF(L11&gt;3,"TEP","TED"))</f>
-        <v>TED</v>
+        <v>TEA</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>6</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>46171</v>
+        <v>46294</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>46220</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H12" s="5"/>
       <c r="I12" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>46220</v>
+        <v>1</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L12" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C12,E12,G12,I12,K12),0)</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M12" s="1" t="str">
         <f aca="false">IF(L12&gt;6,"TEA",IF(L12&gt;3,"TEP","TED"))</f>
-        <v>TEA</v>
+        <v>TEP</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="n">
@@ -4183,62 +4822,101 @@
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="J13" s="1"/>
+        <v>4</v>
+      </c>
       <c r="K13" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L13" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C13,E13,G13,I13,K13),0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M13" s="1" t="str">
         <f aca="false">IF(L13&gt;6,"TEA",IF(L13&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N13" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="R13" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="S13" s="0" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="F14" s="5"/>
+        <v>7</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>46171</v>
+      </c>
       <c r="G14" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="J14" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>46220</v>
+      </c>
       <c r="K14" s="1" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L14" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C14,E14,G14,I14,K14),0)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M14" s="1" t="str">
         <f aca="false">IF(L14&gt;6,"TEA",IF(L14&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N14" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="R14" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="S14" s="0" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="15" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>9</v>
@@ -4248,14 +4926,16 @@
         <v>10</v>
       </c>
       <c r="F15" s="5"/>
-      <c r="G15" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>10</v>
+      <c r="G15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" s="5"/>
+      <c r="I15" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1" t="n">
+        <v>6</v>
       </c>
       <c r="L15" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C15,E15,G15,I15,K15),0)</f>
@@ -4264,6 +4944,24 @@
       <c r="M15" s="1" t="str">
         <f aca="false">IF(L15&gt;6,"TEA",IF(L15&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="XDB15" s="1"/>
       <c r="XDC15" s="1"/>
@@ -4323,104 +5021,137 @@
     </row>
     <row r="16" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>46171</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="D16" s="5"/>
       <c r="E16" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F16" s="5"/>
-      <c r="G16" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>46220</v>
-      </c>
-      <c r="I16" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>46220</v>
-      </c>
-      <c r="K16" s="1" t="n">
-        <v>9</v>
+      <c r="G16" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="L16" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C16,E16,G16,I16,K16),0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M16" s="1" t="str">
         <f aca="false">IF(L16&gt;6,"TEA",IF(L16&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N16" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" s="2"/>
+      <c r="P16" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q16" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="R16" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S16" s="1" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="17" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="D17" s="5"/>
+        <v>7</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>46171</v>
+      </c>
       <c r="E17" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>46171</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F17" s="5"/>
       <c r="G17" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="1" t="n">
-        <v>10</v>
+        <v>3</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>46220</v>
       </c>
       <c r="K17" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L17" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C17,E17,G17,I17,K17),0)</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M17" s="1" t="str">
         <f aca="false">IF(L17&gt;6,"TEA",IF(L17&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N17" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="R17" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S17" s="1" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="18" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C18" s="5" t="n">
         <v>8</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F18" s="5"/>
-      <c r="G18" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>10</v>
+      <c r="G18" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1" t="n">
+        <v>7</v>
       </c>
       <c r="L18" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C18,E18,G18,I18,K18),0)</f>
@@ -4429,6 +5160,24 @@
       <c r="M18" s="1" t="str">
         <f aca="false">IF(L18&gt;6,"TEA",IF(L18&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="XDB18" s="1"/>
       <c r="XDC18" s="1"/>
@@ -4488,35 +5237,55 @@
     </row>
     <row r="19" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>10</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F19" s="5"/>
-      <c r="G19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K19" s="2" t="n">
+      <c r="G19" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="I19" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1" t="n">
         <v>10</v>
       </c>
       <c r="L19" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C19,E19,G19,I19,K19),0)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M19" s="1" t="str">
         <f aca="false">IF(L19&gt;6,"TEA",IF(L19&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="XDB19" s="1"/>
       <c r="XDC19" s="1"/>
@@ -4576,176 +5345,225 @@
     </row>
     <row r="20" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D20" s="5"/>
+        <v>8</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>46171</v>
+      </c>
       <c r="E20" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F20" s="5"/>
-      <c r="G20" s="5" t="n">
+      <c r="G20" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="H20" s="5"/>
-      <c r="I20" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="K20" s="1" t="n">
+      <c r="H20" s="2"/>
+      <c r="I20" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2" t="n">
         <v>10</v>
       </c>
       <c r="L20" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C20,E20,G20,I20,K20),0)</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M20" s="1" t="str">
         <f aca="false">IF(L20&gt;6,"TEA",IF(L20&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="P20" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="R20" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S20" s="1" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="21" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" s="1" t="n">
-        <v>8</v>
+      <c r="A21" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="10"/>
+      <c r="I21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="L21" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C21,E21,G21,I21,K21),0)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M21" s="1" t="str">
         <f aca="false">IF(L21&gt;6,"TEA",IF(L21&gt;3,"TEP","TED"))</f>
-        <v>TEP</v>
-      </c>
-    </row>
-    <row r="22" s="7" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="9"/>
-      <c r="I22" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="L22" s="7" t="n">
+        <v>TED</v>
+      </c>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+    </row>
+    <row r="22" s="8" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="5"/>
+      <c r="I22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C22,E22,G22,I22,K22),0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22" s="1" t="str">
         <f aca="false">IF(L22&gt;6,"TEA",IF(L22&gt;3,"TEP","TED"))</f>
         <v>TED</v>
       </c>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
     </row>
     <row r="23" s="1" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="D23" s="5"/>
+        <v>7</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>46171</v>
+      </c>
       <c r="E23" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="H23" s="5"/>
+        <v>6</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>46220</v>
+      </c>
       <c r="I23" s="1" t="n">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>46220</v>
       </c>
       <c r="K23" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L23" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C23,E23,G23,I23,K23),0)</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M23" s="1" t="str">
         <f aca="false">IF(L23&gt;6,"TEA",IF(L23&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N23" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="P23" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="R23" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="S23" s="1" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="24" s="2" customFormat="true" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>46171</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="I24" s="2" t="n">
+      <c r="A24" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="10"/>
+      <c r="E24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="8"/>
+      <c r="G24" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="10"/>
+      <c r="I24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="K24" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="L24" s="1" t="n">
+      <c r="L24" s="8" t="n">
         <f aca="false">ROUND(AVERAGE(C24,E24,G24,I24,K24),0)</f>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M24" s="1" t="str">
         <f aca="false">IF(L24&gt;6,"TEA",IF(L24&gt;3,"TEP","TED"))</f>
-        <v>TEA</v>
-      </c>
+        <v>TED</v>
+      </c>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
       <c r="XDB24" s="1"/>
       <c r="XDC24" s="1"/>
       <c r="XDD24" s="1"/>
@@ -4804,46 +5622,38 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>46171</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>46171</v>
+        <v>10</v>
+      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="1" t="n">
+        <v>10</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>46171</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="H25" s="5"/>
       <c r="I25" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>46171</v>
+        <v>10</v>
       </c>
       <c r="K25" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L25" s="1" t="n">
         <f aca="false">ROUND(AVERAGE(C25,E25,G25,I25,K25),0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M25" s="1" t="str">
         <f aca="false">IF(L25&gt;6,"TEA",IF(L25&gt;3,"TEP","TED"))</f>
         <v>TEA</v>
       </c>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="2"/>
@@ -4928,7 +5738,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>11</v>
@@ -5073,16 +5883,16 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5120,10 +5930,10 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="1" t="n">
@@ -5521,19 +6331,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5972,16 +6782,16 @@
         <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6019,10 +6829,10 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D4" s="1" t="n">
